--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -11309,12 +11309,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>把握しているのは全国平均・北海道平均・全国での位置までであり、個々の市町村の得点を持っていません。全国集計結果の原本には市町村ごとの行がありますが、構成町から広域連合を割り出す対応表がありません。</t>
+          <t>収録しているのは全国平均・北海道平均・全国での位置までであり、個々の市町村の得点を収録していません。全国集計結果の原本には広域連合・一部事務組合の行があり（名称が市・区・町・村で終わらない行）、並べ替えれば団体の一覧を作れます。ただし当連合の行は3か年とも得点欄が空欄で、構成3町それぞれの行に得点が記載されています。得点のある行は3か年とも1,741で全国の市区町村の数と一致するため、他の広域連合の行も空欄である可能性が高いものの、確かめられていません。</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>確認事項No.168。全国集計結果の原本（令和8年度）と、北海道内の広域連合・一部事務組合とその構成市町村の一覧。</t>
+          <t>確認事項No.168。全国集計結果の原本の再提供と、市町村の行に保険者番号（広域連合の番号）の列があるかの確認。当該列があれば構成市町村の対応表はその列から作れます。</t>
         </is>
       </c>
     </row>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上と同じ理由により、母集団を作れません。</t>
+          <t>上のとおり団体の一覧は原本から作れますが、得点は構成市町村の側にあるため、どの市町村がどの団体を構成するかが分からないと平均が出せません。</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>同上（No.168）。母集団が定まれば、構成町の得点を平均して団体単位の比較ができます。</t>
+          <t>同上（No.168）。母集団が定まれば、構成市町村の得点を平均して団体単位の比較ができます。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,7 +214,20 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,6 +252,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -750,17 +766,17 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>個々の団体の得点</t>
+          <t>同様の構成の団体との比較</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>北海道内の個々の保険者・広域連合の得点は把握できていません。確認できるのは全国平均・北海道平均（179市町村）・全国での位置までです。</t>
+          <t>全国集計には広域連合・一部事務組合の行があります（名称が市・区・町・村で終わらない行）。団体の行に得点はありませんが、直後に続く構成市町村の行から構成を読み取れるため、構成市町村の得点の平均により比べられます。</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>同様の構成の団体との比較は確認事項No.168としてご提供を依頼します（06シート）。</t>
+          <t>38団体・205市町村を割り当てました（06シート）。令和6年度の団体別の値と、団体名を成果品に掲げることの可否は確認事項No.168です。</t>
         </is>
       </c>
     </row>
@@ -915,12 +931,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>できる比較と、できない理由</t>
+          <t>広域連合・一部事務組合38団体と構成市町村205の得点</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>個々の団体の得点は未把握。No.168</t>
+          <t>当連合は38団体中36位、町村のみ11団体中10位</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1960,7 @@
       <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>可</t>
         </is>
@@ -1970,7 +1986,7 @@
       <c r="J25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>条件付き</t>
         </is>
@@ -1996,7 +2012,7 @@
       <c r="J26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>現時点では不可</t>
         </is>
@@ -3442,17 +3458,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>北海道内の同様の構成の団体の得点の抽出（全国集計結果の原本）</t>
+          <t>同様の構成の団体との比較（令和6年度の原本と団体名の掲載）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部確認済み</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -3530,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3925,16 +3941,16 @@
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>19施策のすべてに第10期の基本目標の対照があること</t>
+          <t>広域連合・一部事務組合の行に得点がないこと</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>対照のないものなし</t>
+          <t>38団体</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
@@ -3945,16 +3961,16 @@
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>介護給付費の適正化が第10期の基本目標5に移ることを反映していること</t>
+          <t>構成市町村の数が全国集計の行数と整合すること</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>施策4-3→第5章 基本目標5</t>
+          <t>1,741（得点のある行）＋38（団体の行）＝1779</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
@@ -3965,15 +3981,147 @@
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>当連合の構成市町村が東川町・美瑛町・東神楽町であること</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>東川町・美瑛町・東神楽町</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>当連合の構成市町村の得点が収録値と一致すること（令和8年度）</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>当連合の構成市町村の得点が収録値と一致すること（令和7年度）</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>当連合の平均が3町平均と一致すること</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>334.0</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>団体の順位づけに重複・欠落がないこと</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>全38団体・町村のみ11団体・北海道4団体</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>19施策のすべてに第10期の基本目標の対照があること</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>対照のないものなし</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>介護給付費の適正化が第10期の基本目標5に移ることを反映していること</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>施策4-3→第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>受託者の内部の仕組みの語を本文に書いていないこと</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -11163,228 +11311,3196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>同様の構成の団体との比較（できる比較と、できない理由）</t>
+          <t>同様の構成の団体との比較（広域連合・一部事務組合 38団体）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>北海道内及び管内の、当連合と同様に複数町村で構成する広域連合・一部事務組合との比較についてです。現時点でできる比較と、行うために必要な資料を示します。</t>
+          <t>当連合と同じく複数の市町村で構成する広域連合・一部事務組合は全国に38団体あり、205市町村が属しています。交付金は市町村に交付されるため団体の行に得点はなく、構成市町村の得点の平均により比較します。平均は単純平均です（第1号被保険者数で加重した値も併せて掲げます）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>① 現時点でできる比較</t>
+          <t>① 団体と構成市町村の割り出し方</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>比較の相手</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>確かめたこと</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>令和8年度の結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>全国平均</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>全国1,741市町村の推進・支援合計の平均。</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>全国454.9点に対し3町平均334.0点（対全国比73.4％）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>北海道平均</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>北海道内179市町村の平均。</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>北海道432.6点に対し3町平均334.0点（対北海道比77.2％）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>全国での位置</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>推進・支援合計の全国での位置（下位からの割合）。</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>東川町6.7％・美瑛町6.0％・東神楽町20.5％。東川町・美瑛町は全国の下位1割以内。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>構成3町の相互比較</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>同じ広域連合を構成する3町の間の比較。制度・保険者が同じであるため条件がそろっており、得点が分かれる項目は区域内での横展開の余地を示します。</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>明細列299のうち78列で得点が分かれています（08シート）。</t>
-        </is>
-      </c>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>団体の行があること</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>全国集計は1,779行あり、名称が市・区・町・村で終わらない行が38行ある。いずれも保険者番号を持つ広域連合・一部事務組合である。</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="26" t="n"/>
+      <c r="K6" s="26" t="n"/>
+      <c r="L6" s="26" t="n"/>
+      <c r="M6" s="26" t="n"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>団体の行に得点がないこと</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>38団体とも推進・支援合計の欄が空欄である。得点のある行は1,741で、全国の市区町村の数と一致する。交付金が市町村に交付されるためである。</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="26" t="n"/>
+      <c r="G7" s="26" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
+      <c r="L7" s="26" t="n"/>
+      <c r="M7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>構成市町村が読めること</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>団体の行の直後に構成市町村の行が続く。構成市町村の行は保険者番号の欄が空欄である（保険者番号は団体が持つ）。次に保険者番号のある行が現れるまでが一つの団体である。</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="26" t="n"/>
+      <c r="G8" s="26" t="n"/>
+      <c r="H8" s="26" t="n"/>
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="26" t="n"/>
+      <c r="M8" s="26" t="n"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>漏れがないこと</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>この規則により38団体・205市町村を割り当て、所属の定まらない行は1件もなかった。当連合の構成が東川町・美瑛町・東神楽町となることは既に確認している事実と一致する。</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="26" t="n"/>
+      <c r="G9" s="26" t="n"/>
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="26" t="n"/>
+      <c r="J9" s="26" t="n"/>
+      <c r="K9" s="26" t="n"/>
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="26" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>② 現時点でできない比較と、そのために必要な資料</t>
+          <t>② 38団体の比較（令和8年度・単純平均の高い順）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>行えないこと</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>理由</t>
+          <t>団体</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>必要な資料・確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>北海道内の個々の保険者・広域連合の得点の抽出</t>
-        </is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>構成</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>市を含む</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>R7平均</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>R8平均</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>R7→R8</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>加重平均</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>最低</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>当連合との差</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>収録しているのは全国平均・北海道平均・全国での位置までであり、個々の市町村の得点を収録していません。全国集計結果の原本には広域連合・一部事務組合の行があり（名称が市・区・町・村で終わらない行）、並べ替えれば団体の一覧を作れます。ただし当連合の行は3か年とも得点欄が空欄で、構成3町それぞれの行に得点が記載されています。得点のある行は3か年とも1,741で全国の市区町村の数と一致するため、他の広域連合の行も空欄である可能性が高いものの、確かめられていません。</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>確認事項No.168。全国集計結果の原本の再提供と、市町村の行に保険者番号（広域連合の番号）の列があるかの確認。当該列があれば構成市町村の対応表はその列から作れます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>同様の構成の団体の中での順位づけ</t>
-        </is>
+          <t>浜田地区広域行政組合</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>533.5</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>644.5</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>+111.0</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>639.9</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>632</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>657</v>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>+310.5</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上のとおり団体の一覧は原本から作れますが、得点は構成市町村の側にあるため、どの市町村がどの団体を構成するかが分からないと平均が出せません。</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>同上（No.168）。母集団が定まれば、構成市町村の得点を平均して団体単位の比較ができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>得点の高い団体の計画を参照して必要項目を導くこと</t>
-        </is>
+          <t>大曲仙北広域市町村圏組合</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>518.7</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>604</v>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>+85.3</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>599</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>591</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>621</v>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>+270.0</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>他団体の資料は成果品に用いず、記載の借用も行わないというご指示によるものです。</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>代わりに、評価指標の原典に示された明細列と全国該当率により「全国の標準」を導いています（07シート）。こちらは公表されている評価指標と全国集計だけで完結します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>得点0の理由の判別</t>
-        </is>
+          <t>知多北部広域連合</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>596.2</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>-9.8</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>584.2</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>569</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>612</v>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>+252.5</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>得点0が「取組がない」のか「取組はあるが要件を満たさない」のか「報告していない」のかを、公表資料から判別できません。</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>確認事項No.6（交付金の評価調書）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>【補足】「全国の標準からみた必要項目」（07シート）と「区域内で分かれている項目」（08シート）の2つは、他団体の計画を参照しなくても導けるものです。得点の高い団体の計画を参照して導くものと目的は同じであり、公表されている評価指標と全国集計のみで完結する点で確かです。</t>
-        </is>
-      </c>
+          <t>坂井地区広域連合</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>福井県</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>538</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>582.5</v>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>+44.5</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>587.6</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>572</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>593</v>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>+248.5</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>佐賀中部広域連合</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>佐賀県</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>590</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>576</v>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>-14.0</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>561.5</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>554</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>611</v>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>+242.0</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>安八郡広域連合</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>498.7</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>575.3</v>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>+76.7</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>574.1</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>581</v>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>+241.3</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>空知中部広域連合</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>563.3</v>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>+20.8</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>566.2</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>528</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>615</v>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>+229.3</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>北海道内で最も高い。歌志内市を含む6市町</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>鳥栖地区広域市町村圏組合</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>佐賀県</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>586</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>556.8</v>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>-29.2</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>560.4</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>543</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>+222.8</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>雲南広域連合</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>556</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>540.7</v>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>-15.3</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>534</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>529</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>553</v>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>+206.7</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>木曽広域連合</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>518.8</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>526.7</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>494</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>+201.8</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>杵藤地区広域市町村圏組合</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>佐賀県</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>472.1</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>528.7</v>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>+56.6</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>522.6</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>594</v>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>+194.7</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>隠岐広域連合</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>451.5</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>520.8</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>+69.2</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>498.2</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>486</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>549</v>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>+186.8</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>福岡県介護保険広域連合</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>522.1</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>510.3</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>-11.8</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>567</v>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>+176.3</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>鈴鹿亀山地区広域連合</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>503.5</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>505.5</v>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>509.9</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>498</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>513</v>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>+171.5</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>中新川広域行政事務組合</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>富山県</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>494</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>497.7</v>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>+3.7</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>475.8</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>545</v>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>+163.7</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>紀南介護保険広域連合</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>496.7</v>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>+111.3</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>492.6</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>479</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>506</v>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>+162.7</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>大里広域市町村圏組合</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>474.3</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>493.7</v>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>+19.3</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>509.2</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>435</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>557</v>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>+159.7</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>日高中部広域連合</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>471.5</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>+20.5</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>521</v>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>+158.0</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>構成2町。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>島原地域広域市町村圏組合</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>長崎県</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>583</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>488.7</v>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>-94.3</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>488.4</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>505</v>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>+154.7</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>砺波地方介護保険組合</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>富山県</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>512.3</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>481.7</v>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>-30.7</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>482.3</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>475</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>488</v>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>+147.7</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>南部箕蚊屋広域連合</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>鳥取県</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>456.7</v>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>+15.0</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>458.6</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>451</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>+122.7</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>北アルプス広域連合</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>428</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>453.4</v>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>+25.4</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>442.1</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>488</v>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>+119.4</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>後志広域連合</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>421.1</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>+15.4</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>535</v>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>+102.4</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>構成16町村。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>新川地域介護保険・ケーブルテレビ事業組合</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>富山県</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>412</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>434</v>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>+22.0</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>421</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>458</v>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>+100.0</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>紀北広域連合</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>459</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>430.5</v>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>-28.5</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>453</v>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>+96.5</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>二戸地区広域行政事務組合</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>447</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>426.2</v>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>-20.8</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>416</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>439</v>
+      </c>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>+92.2</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>諏訪広域連合</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>428.7</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>-10.0</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>429.7</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>367</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>447</v>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>+84.7</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>東三河広域連合</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>401.2</v>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>+56.9</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>414</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>327</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>459</v>
+      </c>
+      <c r="L40" s="13" t="inlineStr">
+        <is>
+          <t>+67.2</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>揖斐広域連合</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>390</v>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>+12.7</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>321</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>+56.0</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>久慈広域連合</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>+17.8</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>427.7</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>475</v>
+      </c>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>+41.0</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>みよし広域連合</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>徳島県</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>342</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>374</v>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>+32.0</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>356</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="L43" s="13" t="inlineStr">
+        <is>
+          <t>+40.0</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>もとす広域連合</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>-11.3</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>+37.3</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>盛岡北部行政事務組合</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>313</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>354</v>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>+41.0</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>+20.0</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>中芸広域連合</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>352</v>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>+60.4</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="L46" s="13" t="inlineStr">
+        <is>
+          <t>+18.0</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>沖縄県介護保険広域連合</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>+16.3</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>+11.2</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>334</v>
+      </c>
+      <c r="H48" s="28" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>308</v>
+      </c>
+      <c r="K48" s="8" t="n">
+        <v>379</v>
+      </c>
+      <c r="L48" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>当連合。令和7年度から横ばいで、団体の平均が上がる中で位置が下がった</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>一関地区広域行政組合</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>342</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>-26.5</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>314</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="L49" s="13" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>邑智郡総合事務組合</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>291.3</v>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>-37.0</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>268.9</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>337</v>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>-42.7</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>【読み取り】当連合は38団体中36位です。38団体の平均は令和7年度450.7点から令和8年度466.9点へ+16.1点上がっているのに対し、当連合は335.3点から334.0点へ-1.3点で、団体の側でも同じ傾きの差が出ています。構成市町村の最低は308点・最高は379点で、区域内の開きは71点です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>③ 同様の構成（町村のみで構成する団体）との比較</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>団体</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>構成</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>市を含む</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>R7平均</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>R8平均</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>R7→R8</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>加重平均</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>最低</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>当連合との差</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>安八郡広域連合</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>498.7</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>575.3</v>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>+76.7</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>574.1</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>581</v>
+      </c>
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>+241.3</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>木曽広域連合</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>518.8</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>526.7</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>494</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="L56" s="13" t="inlineStr">
+        <is>
+          <t>+201.8</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>隠岐広域連合</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>451.5</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>520.8</v>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>+69.2</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>498.2</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>486</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>549</v>
+      </c>
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>+186.8</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>中新川広域行政事務組合</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>富山県</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>494</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>497.7</v>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>+3.7</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>475.8</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>545</v>
+      </c>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>+163.7</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>日高中部広域連合</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>471.5</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>+20.5</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>521</v>
+      </c>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>+158.0</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>構成2町。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>南部箕蚊屋広域連合</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>鳥取県</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>456.7</v>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>+15.0</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>458.6</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>451</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>+122.7</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>後志広域連合</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>421.1</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>+15.4</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>535</v>
+      </c>
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>+102.4</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>構成16町村。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>揖斐広域連合</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>390</v>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>+12.7</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>321</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>+56.0</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>中芸広域連合</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>352</v>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>+60.4</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>+18.0</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="G64" s="21" t="n">
+        <v>334</v>
+      </c>
+      <c r="H64" s="28" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>308</v>
+      </c>
+      <c r="K64" s="8" t="n">
+        <v>379</v>
+      </c>
+      <c r="L64" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="inlineStr">
+        <is>
+          <t>当連合。令和7年度から横ばいで、団体の平均が上がる中で位置が下がった</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>邑智郡総合事務組合</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>291.3</v>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>-37.0</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>268.9</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>337</v>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>-42.7</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>【読み取り】市を含まず町村のみで構成する団体は11団体あり、当連合はその中で10位です。11団体の平均は443.8点で、当連合は109.8点低くなっています。令和7年度から下がったのは2団体だけです。町村のみで構成することが低位の理由にはなっていません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>④ 北海道内の団体</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>団体</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>構成</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>市を含む</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>R7平均</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>R8平均</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>R7→R8</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>加重平均</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>最低</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>当連合との差</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>構成市町村</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>空知中部広域連合</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>563.3</v>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>+20.8</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>566.2</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>528</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>615</v>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>+229.3</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>歌志内市・奈井江町・上砂川町・浦臼町・新十津川町・雨竜町</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>日高中部広域連合</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>471.5</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>+20.5</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>521</v>
+      </c>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>+158.0</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>新冠町・新ひだか町</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>後志広域連合</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>421.1</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>+15.4</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>535</v>
+      </c>
+      <c r="L72" s="13" t="inlineStr">
+        <is>
+          <t>+102.4</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>島牧村・黒松内町・蘭越町・ニセコ町・真狩村・留寿都村・喜茂別町・京極町・倶知安町・共和町・泊村・神恵内村・積丹町・古平町・仁木町・赤井川村</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="29" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="G73" s="21" t="n">
+        <v>334</v>
+      </c>
+      <c r="H73" s="28" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>308</v>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>379</v>
+      </c>
+      <c r="L73" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="inlineStr">
+        <is>
+          <t>東川町・美瑛町・東神楽町</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>【読み取り】北海道内の団体は4件で、当連合は最も低い水準です。最も高い空知中部広域連合とは229.3点の差があります。後志広域連合・日高中部広域連合は当連合と同じく町村のみで構成しますが、いずれも当連合を上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>⑤ なお確かめられていないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>令和6年度の団体別の値</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>受領した原本は令和8年度の集計で、令和7年度の合計得点は併載されているが令和6年度はない。3か年の推移を団体別に示すには令和6年度の原本を要する（確認事項No.168）。</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="n"/>
+      <c r="D78" s="26" t="n"/>
+      <c r="E78" s="26" t="n"/>
+      <c r="F78" s="26" t="n"/>
+      <c r="G78" s="26" t="n"/>
+      <c r="H78" s="26" t="n"/>
+      <c r="I78" s="26" t="n"/>
+      <c r="J78" s="26" t="n"/>
+      <c r="K78" s="26" t="n"/>
+      <c r="L78" s="26" t="n"/>
+      <c r="M78" s="26" t="n"/>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>団体名を成果品に掲げること</t>
+        </is>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>本シートの団体名は公表されている全国集計の行の名称であり、他団体が策定した計画その他の資料によるものではない。成果品に団体名を掲げてよいかをご確認いただきたい（確認事項No.168）。</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="n"/>
+      <c r="D79" s="26" t="n"/>
+      <c r="E79" s="26" t="n"/>
+      <c r="F79" s="26" t="n"/>
+      <c r="G79" s="26" t="n"/>
+      <c r="H79" s="26" t="n"/>
+      <c r="I79" s="26" t="n"/>
+      <c r="J79" s="26" t="n"/>
+      <c r="K79" s="26" t="n"/>
+      <c r="L79" s="26" t="n"/>
+      <c r="M79" s="26" t="n"/>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>得点0の理由</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>他団体についても、得点0が「取組がない」のか「要件を満たさない」のかは公表資料から判別できない。得点の差をそのまま取組の差と読まない（確認事項No.6）。</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="n"/>
+      <c r="D80" s="26" t="n"/>
+      <c r="E80" s="26" t="n"/>
+      <c r="F80" s="26" t="n"/>
+      <c r="G80" s="26" t="n"/>
+      <c r="H80" s="26" t="n"/>
+      <c r="I80" s="26" t="n"/>
+      <c r="J80" s="26" t="n"/>
+      <c r="K80" s="26" t="n"/>
+      <c r="L80" s="26" t="n"/>
+      <c r="M80" s="26" t="n"/>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>平均の置き方</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>本シートは構成市町村の単純平均を主とし、第1号被保険者数で加重した値を併せて掲げた。構成市町村の数と規模が団体により大きく異なるため、どちらを用いるかで順位が入れ替わる団体がある。</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
+      <c r="G81" s="26" t="n"/>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="26" t="n"/>
+      <c r="J81" s="26" t="n"/>
+      <c r="K81" s="26" t="n"/>
+      <c r="L81" s="26" t="n"/>
+      <c r="M81" s="26" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="17">
+    <mergeCell ref="B6:M6"/>
+    <mergeCell ref="A76:M76"/>
+    <mergeCell ref="A68:M68"/>
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="B78:M78"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="B81:M81"/>
+    <mergeCell ref="B80:M80"/>
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="A53:M53"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="B79:M79"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A11:M11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 &amp;A　&amp;P/&amp;N</oddFooter>
@@ -12354,7 +15470,7 @@
       <c r="F26" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="30" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -12396,7 +15512,7 @@
       <c r="F27" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="30" t="n">
         <v>91.90000000000001</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -12438,7 +15554,7 @@
       <c r="F28" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="30" t="n">
         <v>88</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -12480,7 +15596,7 @@
       <c r="F29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="30" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -12522,7 +15638,7 @@
       <c r="F30" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="30" t="n">
         <v>85.3</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -12564,7 +15680,7 @@
       <c r="F31" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="30" t="n">
         <v>83.5</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -12606,7 +15722,7 @@
       <c r="F32" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="30" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -12648,7 +15764,7 @@
       <c r="F33" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="30" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -12690,7 +15806,7 @@
       <c r="F34" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="30" t="n">
         <v>80</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -12732,7 +15848,7 @@
       <c r="F35" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="30" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -12774,7 +15890,7 @@
       <c r="F36" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="30" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -12816,7 +15932,7 @@
       <c r="F37" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="30" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -12858,7 +15974,7 @@
       <c r="F38" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G38" s="30" t="n">
         <v>76.3</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -12900,7 +16016,7 @@
       <c r="F39" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G39" s="30" t="n">
         <v>75.8</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -12942,7 +16058,7 @@
       <c r="F40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="30" t="n">
         <v>71</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -12984,7 +16100,7 @@
       <c r="F41" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="30" t="n">
         <v>70.5</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -13026,7 +16142,7 @@
       <c r="F42" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="30" t="n">
         <v>70</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -13068,7 +16184,7 @@
       <c r="F43" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="25" t="n">
+      <c r="G43" s="30" t="n">
         <v>70</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -13110,7 +16226,7 @@
       <c r="F44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="30" t="n">
         <v>70</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -13152,7 +16268,7 @@
       <c r="F45" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="26" t="n">
+      <c r="G45" s="31" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -13194,7 +16310,7 @@
       <c r="F46" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G46" s="26" t="n">
+      <c r="G46" s="31" t="n">
         <v>64.5</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -13236,7 +16352,7 @@
       <c r="F47" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G47" s="26" t="n">
+      <c r="G47" s="31" t="n">
         <v>62.1</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -13278,7 +16394,7 @@
       <c r="F48" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G48" s="26" t="n">
+      <c r="G48" s="31" t="n">
         <v>61.3</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -13320,7 +16436,7 @@
       <c r="F49" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G49" s="26" t="n">
+      <c r="G49" s="31" t="n">
         <v>60.4</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -13362,7 +16478,7 @@
       <c r="F50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="26" t="n">
+      <c r="G50" s="31" t="n">
         <v>59</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
@@ -13404,7 +16520,7 @@
       <c r="F51" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="26" t="n">
+      <c r="G51" s="31" t="n">
         <v>58.2</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -13446,7 +16562,7 @@
       <c r="F52" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G52" s="26" t="n">
+      <c r="G52" s="31" t="n">
         <v>57.1</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -13488,7 +16604,7 @@
       <c r="F53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="26" t="n">
+      <c r="G53" s="31" t="n">
         <v>54.9</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -13530,7 +16646,7 @@
       <c r="F54" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="26" t="n">
+      <c r="G54" s="31" t="n">
         <v>53.4</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -13572,7 +16688,7 @@
       <c r="F55" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G55" s="26" t="n">
+      <c r="G55" s="31" t="n">
         <v>52.9</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -13614,7 +16730,7 @@
       <c r="F56" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="26" t="n">
+      <c r="G56" s="31" t="n">
         <v>51.2</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -13656,7 +16772,7 @@
       <c r="F57" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="26" t="n">
+      <c r="G57" s="31" t="n">
         <v>50.6</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -13698,7 +16814,7 @@
       <c r="F58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G58" s="26" t="n">
+      <c r="G58" s="31" t="n">
         <v>50.3</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -13740,7 +16856,7 @@
       <c r="F59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="26" t="n">
+      <c r="G59" s="31" t="n">
         <v>50.3</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -13782,7 +16898,7 @@
       <c r="F60" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G60" s="26" t="n">
+      <c r="G60" s="31" t="n">
         <v>50.1</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -13824,7 +16940,7 @@
       <c r="F61" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G61" s="26" t="n">
+      <c r="G61" s="31" t="n">
         <v>50</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -13866,7 +16982,7 @@
       <c r="F62" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="26" t="n">
+      <c r="G62" s="31" t="n">
         <v>50</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -13908,7 +17024,7 @@
       <c r="F63" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G63" s="26" t="n">
+      <c r="G63" s="31" t="n">
         <v>50</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -14038,19 +17154,19 @@
           <t>東川町</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="32" t="n">
         <v>315</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>56</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="33" t="n">
         <v>109</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>85</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="34" t="n">
         <v>240</v>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -14066,19 +17182,19 @@
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="32" t="n">
         <v>308</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="33" t="n">
         <v>116</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>83</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="34" t="n">
         <v>254</v>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -14094,19 +17210,19 @@
           <t>東神楽町</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="32" t="n">
         <v>379</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="33" t="n">
         <v>45</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="34" t="n">
         <v>184</v>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -14219,7 +17335,7 @@
       <c r="F13" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="35" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="H13" s="17" t="n">
@@ -14269,7 +17385,7 @@
       <c r="F14" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="35" t="n">
         <v>47.3</v>
       </c>
       <c r="H14" s="17" t="n">
@@ -14319,7 +17435,7 @@
       <c r="F15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="35" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="H15" s="17" t="n">
@@ -14369,7 +17485,7 @@
       <c r="F16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="35" t="n">
         <v>87.8</v>
       </c>
       <c r="H16" s="14" t="n">
@@ -14419,7 +17535,7 @@
       <c r="F17" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G17" s="30" t="n">
+      <c r="G17" s="35" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="H17" s="14" t="n">
@@ -14469,7 +17585,7 @@
       <c r="F18" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="30" t="n">
+      <c r="G18" s="35" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="H18" s="14" t="n">
@@ -14519,7 +17635,7 @@
       <c r="F19" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G19" s="35" t="n">
         <v>46.1</v>
       </c>
       <c r="H19" s="14" t="n">
@@ -14569,7 +17685,7 @@
       <c r="F20" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="35" t="n">
         <v>43.1</v>
       </c>
       <c r="H20" s="17" t="n">
@@ -14619,7 +17735,7 @@
       <c r="F21" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="30" t="n">
+      <c r="G21" s="35" t="n">
         <v>74.5</v>
       </c>
       <c r="H21" s="17" t="n">
@@ -14669,7 +17785,7 @@
       <c r="F22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="30" t="n">
+      <c r="G22" s="35" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="H22" s="14" t="n">
@@ -14719,7 +17835,7 @@
       <c r="F23" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="30" t="n">
+      <c r="G23" s="35" t="n">
         <v>48.8</v>
       </c>
       <c r="H23" s="14" t="n">
@@ -14769,7 +17885,7 @@
       <c r="F24" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="30" t="n">
+      <c r="G24" s="35" t="n">
         <v>87</v>
       </c>
       <c r="H24" s="14" t="n">
@@ -14819,7 +17935,7 @@
       <c r="F25" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="30" t="n">
+      <c r="G25" s="35" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="H25" s="17" t="n">
@@ -14869,7 +17985,7 @@
       <c r="F26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="30" t="n">
+      <c r="G26" s="35" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="H26" s="14" t="n">
@@ -14919,7 +18035,7 @@
       <c r="F27" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="30" t="n">
+      <c r="G27" s="35" t="n">
         <v>70.5</v>
       </c>
       <c r="H27" s="14" t="n">
@@ -14965,7 +18081,7 @@
       <c r="F28" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G28" s="30" t="n">
+      <c r="G28" s="35" t="n">
         <v>70.5</v>
       </c>
       <c r="H28" s="14" t="n">
@@ -15011,7 +18127,7 @@
       <c r="F29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="30" t="n">
+      <c r="G29" s="35" t="n">
         <v>70</v>
       </c>
       <c r="H29" s="17" t="n">
@@ -15057,7 +18173,7 @@
       <c r="F30" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="30" t="n">
+      <c r="G30" s="35" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="H30" s="14" t="n">
@@ -15103,7 +18219,7 @@
       <c r="F31" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="30" t="n">
+      <c r="G31" s="35" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="H31" s="14" t="n">
@@ -15149,7 +18265,7 @@
       <c r="F32" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="30" t="n">
+      <c r="G32" s="35" t="n">
         <v>50</v>
       </c>
       <c r="H32" s="14" t="n">
@@ -15195,7 +18311,7 @@
       <c r="F33" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="30" t="n">
+      <c r="G33" s="35" t="n">
         <v>50</v>
       </c>
       <c r="H33" s="17" t="n">
@@ -15241,7 +18357,7 @@
       <c r="F34" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G34" s="30" t="n">
+      <c r="G34" s="35" t="n">
         <v>46.2</v>
       </c>
       <c r="H34" s="17" t="n">
@@ -15287,7 +18403,7 @@
       <c r="F35" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="30" t="n">
+      <c r="G35" s="35" t="n">
         <v>30</v>
       </c>
       <c r="H35" s="14" t="n">
@@ -15333,7 +18449,7 @@
       <c r="F36" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="30" t="n">
+      <c r="G36" s="35" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="H36" s="17" t="n">
@@ -15379,7 +18495,7 @@
       <c r="F37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="30" t="n">
+      <c r="G37" s="35" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="H37" s="17" t="n">
@@ -15425,7 +18541,7 @@
       <c r="F38" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="30" t="n">
+      <c r="G38" s="35" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="H38" s="17" t="n">
@@ -15471,7 +18587,7 @@
       <c r="F39" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="30" t="n">
+      <c r="G39" s="35" t="n">
         <v>83.2</v>
       </c>
       <c r="H39" s="17" t="n">
@@ -15521,7 +18637,7 @@
       <c r="F40" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="30" t="n">
+      <c r="G40" s="35" t="n">
         <v>82.7</v>
       </c>
       <c r="H40" s="14" t="n">
@@ -15567,7 +18683,7 @@
       <c r="F41" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="30" t="n">
+      <c r="G41" s="35" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="H41" s="14" t="n">
@@ -15613,7 +18729,7 @@
       <c r="F42" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="30" t="n">
+      <c r="G42" s="35" t="n">
         <v>81.8</v>
       </c>
       <c r="H42" s="17" t="n">
@@ -15659,7 +18775,7 @@
       <c r="F43" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="30" t="n">
+      <c r="G43" s="35" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="H43" s="17" t="n">
@@ -15705,7 +18821,7 @@
       <c r="F44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="30" t="n">
+      <c r="G44" s="35" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="H44" s="17" t="n">
@@ -15751,7 +18867,7 @@
       <c r="F45" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="30" t="n">
+      <c r="G45" s="35" t="n">
         <v>71.2</v>
       </c>
       <c r="H45" s="17" t="n">
@@ -15797,7 +18913,7 @@
       <c r="F46" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G46" s="30" t="n">
+      <c r="G46" s="35" t="n">
         <v>70</v>
       </c>
       <c r="H46" s="17" t="n">
@@ -15843,7 +18959,7 @@
       <c r="F47" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G47" s="30" t="n">
+      <c r="G47" s="35" t="n">
         <v>70</v>
       </c>
       <c r="H47" s="14" t="n">
@@ -15889,7 +19005,7 @@
       <c r="F48" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="30" t="n">
+      <c r="G48" s="35" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="H48" s="17" t="n">
@@ -15935,7 +19051,7 @@
       <c r="F49" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G49" s="30" t="n">
+      <c r="G49" s="35" t="n">
         <v>61.2</v>
       </c>
       <c r="H49" s="17" t="n">
@@ -15981,7 +19097,7 @@
       <c r="F50" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G50" s="30" t="n">
+      <c r="G50" s="35" t="n">
         <v>50.1</v>
       </c>
       <c r="H50" s="17" t="n">
@@ -16027,7 +19143,7 @@
       <c r="F51" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="30" t="n">
+      <c r="G51" s="35" t="n">
         <v>50.1</v>
       </c>
       <c r="H51" s="17" t="n">
@@ -16073,7 +19189,7 @@
       <c r="F52" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="30" t="n">
+      <c r="G52" s="35" t="n">
         <v>47.7</v>
       </c>
       <c r="H52" s="17" t="n">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>38団体・205市町村を割り当てました（06シート）。令和6年度の団体別の値と、団体名を成果品に掲げることの可否は確認事項No.168です。</t>
+          <t>38団体・205市町村を割り当て、令和6年度から令和8年度までの3か年で比べました（06シート）。団体名を成果品に掲げることの可否は確認事項No.168です。</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>広域連合・一部事務組合38団体と構成市町村205の得点</t>
+          <t>広域連合・一部事務組合38団体と構成市町村205の3か年の得点</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>当連合は38団体中36位、町村のみ11団体中10位</t>
+          <t>当連合は38団体中36位、町村のみ11団体中10位、北海道内4団体で最下位</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>同様の構成の団体との比較（令和6年度の原本と団体名の掲載）</t>
+          <t>同様の構成の団体との比較（団体名の掲載と令和7年度の内訳）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3546,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>当連合の構成市町村の得点が収録値と一致すること（令和7年度）</t>
+          <t>当連合の構成市町村の得点が収録値と一致すること（令和6・7年度）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -4033,16 +4033,16 @@
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>当連合の平均が3町平均と一致すること</t>
+          <t>3か年とも38団体の構成市町村が同じであること</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>令和6年度のみの団体2件</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -4053,16 +4053,16 @@
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>団体の順位づけに重複・欠落がないこと</t>
+          <t>当連合の令和6年度の平均が3町平均と一致すること</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>全38団体・町村のみ11団体・北海道4団体</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -4073,16 +4073,16 @@
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>19施策のすべてに第10期の基本目標の対照があること</t>
+          <t>当連合の平均が3町平均と一致すること</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>対照のないものなし</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -4093,16 +4093,16 @@
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>介護給付費の適正化が第10期の基本目標5に移ることを反映していること</t>
+          <t>団体の順位づけに重複・欠落がないこと</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>施策4-3→第5章 基本目標5</t>
+          <t>全38団体・町村のみ11団体・北海道4団体</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -4113,15 +4113,55 @@
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>19施策のすべてに第10期の基本目標の対照があること</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>対照のないものなし</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>介護給付費の適正化が第10期の基本目標5に移ることを反映していること</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>施策4-3→第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>受託者の内部の仕組みの語を本文に書いていないこと</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -11311,7 +11351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11319,14 +11359,15 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -11339,7 +11380,7 @@
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>当連合と同じく複数の市町村で構成する広域連合・一部事務組合は全国に38団体あり、205市町村が属しています。交付金は市町村に交付されるため団体の行に得点はなく、構成市町村の得点の平均により比較します。平均は単純平均です（第1号被保険者数で加重した値も併せて掲げます）。</t>
+          <t>当連合と同じく複数の市町村で構成する広域連合・一部事務組合は全国に38団体あり、205市町村が属しています。交付金は市町村に交付されるため団体の行に得点はなく、構成市町村の得点の平均により比較します。平均は単純平均です（第1号被保険者数で加重した値も併せて掲げます）。令和6年度から令和8年度までの3か年で比べています。</t>
         </is>
       </c>
     </row>
@@ -11376,6 +11417,7 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -11399,6 +11441,7 @@
       <c r="K6" s="26" t="n"/>
       <c r="L6" s="26" t="n"/>
       <c r="M6" s="26" t="n"/>
+      <c r="N6" s="26" t="n"/>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -11422,6 +11465,7 @@
       <c r="K7" s="26" t="n"/>
       <c r="L7" s="26" t="n"/>
       <c r="M7" s="26" t="n"/>
+      <c r="N7" s="26" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -11445,6 +11489,7 @@
       <c r="K8" s="26" t="n"/>
       <c r="L8" s="26" t="n"/>
       <c r="M8" s="26" t="n"/>
+      <c r="N8" s="26" t="n"/>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -11454,7 +11499,7 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>この規則により38団体・205市町村を割り当て、所属の定まらない行は1件もなかった。当連合の構成が東川町・美瑛町・東神楽町となることは既に確認している事実と一致する。</t>
+          <t>この規則により令和8年度は38団体・205市町村、令和6年度は40団体・210市町村を割り当て、所属の定まらない行は1件もなかった。当連合の構成が東川町・美瑛町・東神楽町となることは既に確認している事実と一致する。</t>
         </is>
       </c>
       <c r="C9" s="26" t="n"/>
@@ -11468,293 +11513,283 @@
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="26" t="n"/>
       <c r="M9" s="26" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="N9" s="26" t="n"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>3か年を通して比べられること</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>38団体の構成市町村は令和6年度と令和8年度で完全に一致する（市町村コードで照合）。令和6年度にあって令和8年度にない団体が2件ある。</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="26" t="n"/>
+      <c r="J10" s="26" t="n"/>
+      <c r="K10" s="26" t="n"/>
+      <c r="L10" s="26" t="n"/>
+      <c r="M10" s="26" t="n"/>
+      <c r="N10" s="26" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>② 38団体の比較（令和8年度・単純平均の高い順）</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>団体</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>都道府県</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>構成</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>市を含む</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>R6平均</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>R7平均</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>R8平均</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>R7→R8</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>R6→R8</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>加重平均</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>最低</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>当連合との差</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>見方</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>浜田地区広域行政組合</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>島根県</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>533.5</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>644.5</v>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>+111.0</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>639.9</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>632</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>657</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>+310.5</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>浜田地区広域行政組合</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>大曲仙北広域市町村圏組合</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>秋田県</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>3</v>
-      </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>518.7</v>
+        <v>572.5</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>604</v>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>+85.3</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>599</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>591</v>
+        <v>533.5</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>644.5</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>+72.0</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>639.9</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>621</v>
-      </c>
-      <c r="L14" s="13" t="inlineStr">
-        <is>
-          <t>+270.0</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr"/>
+        <v>632</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>657</v>
+      </c>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>+310.5</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>大曲仙北広域市町村圏組合</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>知多北部広域連合</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>4</v>
-      </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>596.2</v>
+        <v>580.3</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>586.5</v>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>-9.8</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>584.2</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>569</v>
+        <v>518.7</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>604</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>+23.7</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>599</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>612</v>
-      </c>
-      <c r="L15" s="13" t="inlineStr">
-        <is>
-          <t>+252.5</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr"/>
+        <v>591</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>621</v>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>+270.0</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>知多北部広域連合</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>坂井地区広域連合</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>福井県</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>2</v>
-      </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>538</v>
+        <v>608.8</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>582.5</v>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>+44.5</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>587.6</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>572</v>
+        <v>596.2</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>-22.2</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>584.2</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>593</v>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>+248.5</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr"/>
+        <v>569</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>612</v>
+      </c>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>+252.5</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>佐賀中部広域連合</t>
+          <t>坂井地区広域連合</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>福井県</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -11762,150 +11797,155 @@
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>590</v>
+        <v>494.5</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>576</v>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>-14.0</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>561.5</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>554</v>
+        <v>538</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>582.5</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>+88.0</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>587.6</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>611</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>+242.0</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr"/>
+        <v>572</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>593</v>
+      </c>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>+248.5</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>安八郡広域連合</t>
+          <t>佐賀中部広域連合</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>498.7</v>
+        <v>558.2</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>575.3</v>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>+76.7</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>574.1</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>568</v>
+        <v>590</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>576</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>+17.8</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>561.5</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>581</v>
-      </c>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>+241.3</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr"/>
+        <v>554</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>611</v>
+      </c>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>+242.0</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>空知中部広域連合</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>北海道</t>
+          <t>安八郡広域連合</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>542.5</v>
+        <v>487.7</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>563.3</v>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>+20.8</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>566.2</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>528</v>
+        <v>498.7</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>575.3</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>+87.7</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>574.1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>615</v>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>+229.3</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>北海道内で最も高い。歌志内市を含む6市町</t>
-        </is>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>581</v>
+      </c>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>+241.3</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鳥栖地区広域市町村圏組合</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>佐賀県</t>
+          <t>空知中部広域連合</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
@@ -11913,48 +11953,55 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>586</v>
+        <v>545.5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>556.8</v>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>-29.2</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>560.4</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>543</v>
+        <v>542.5</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>563.3</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>+17.8</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>566.2</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>+222.8</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr"/>
+        <v>528</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>615</v>
+      </c>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>+229.3</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>北海道内で最も高い。歌志内市を含む6市町</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>雲南広域連合</t>
+          <t>鳥栖地区広域市町村圏組合</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>島根県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -11962,244 +12009,259 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>556</v>
+        <v>527.5</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>540.7</v>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>-15.3</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>534</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>529</v>
+        <v>586</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>556.8</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>+29.2</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>560.4</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>553</v>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
-          <t>+206.7</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr"/>
+        <v>543</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>+222.8</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>木曽広域連合</t>
+          <t>雲南広域連合</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>518.8</v>
+        <v>583.3</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>535.8</v>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>+17.0</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>526.7</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>494</v>
+        <v>556</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>540.7</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>-42.7</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>534</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>+201.8</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr"/>
+        <v>529</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>553</v>
+      </c>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>+206.7</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>杵藤地区広域市町村圏組合</t>
+          <t>木曽広域連合</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>佐賀県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>472.1</v>
+        <v>452</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>528.7</v>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>+56.6</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>522.6</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>495</v>
+        <v>518.8</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>+83.8</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>526.7</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>594</v>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>+194.7</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr"/>
+        <v>494</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>+201.8</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>隠岐広域連合</t>
+          <t>杵藤地区広域市町村圏組合</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>島根県</t>
+          <t>佐賀県</t>
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>451.5</v>
+        <v>473.7</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>+69.2</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>498.2</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>486</v>
+        <v>472.1</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>528.7</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>+55.0</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>522.6</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>549</v>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>+186.8</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr"/>
+        <v>495</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>594</v>
+      </c>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>+194.7</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>福岡県介護保険広域連合</t>
+          <t>隠岐広域連合</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>福岡県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>522.1</v>
+        <v>488.8</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>510.3</v>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>-11.8</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>512.7</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>426</v>
+        <v>451.5</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>520.8</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>+32.0</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>498.2</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>567</v>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>+176.3</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr"/>
+        <v>486</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>549</v>
+      </c>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>+186.8</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>鈴鹿亀山地区広域連合</t>
+          <t>福岡県介護保険広域連合</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>福岡県</t>
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -12207,93 +12269,99 @@
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>503.5</v>
+        <v>478.9</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>505.5</v>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>509.9</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>498</v>
+        <v>522.1</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>510.3</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>+31.4</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>512.7</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>513</v>
-      </c>
-      <c r="L26" s="13" t="inlineStr">
-        <is>
-          <t>+171.5</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr"/>
+        <v>426</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>567</v>
+      </c>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>+176.3</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>中新川広域行政事務組合</t>
+          <t>鈴鹿亀山地区広域連合</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>富山県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>494</v>
+        <v>389</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>497.7</v>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>475.8</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>463</v>
+        <v>503.5</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>505.5</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>+116.5</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>509.9</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>545</v>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>+163.7</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr"/>
+        <v>498</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>513</v>
+      </c>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>+171.5</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>紀南介護保険広域連合</t>
+          <t>中新川広域行政事務組合</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="D28" s="13" t="n">
@@ -12301,48 +12369,51 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>385.3</v>
+        <v>539</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>496.7</v>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>+111.3</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>492.6</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>479</v>
+        <v>494</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>497.7</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>-41.3</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>475.8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>506</v>
-      </c>
-      <c r="L28" s="13" t="inlineStr">
-        <is>
-          <t>+162.7</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr"/>
+        <v>463</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>545</v>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>+163.7</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>大里広域市町村圏組合</t>
+          <t>紀南介護保険広域連合</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>埼玉県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
@@ -12354,146 +12425,155 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>474.3</v>
+        <v>392.3</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>493.7</v>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>+19.3</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>509.2</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>435</v>
+        <v>385.3</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>496.7</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>+104.3</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>492.6</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>557</v>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>+159.7</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr"/>
+        <v>479</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>506</v>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>+162.7</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>日高中部広域連合</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>北海道</t>
+          <t>大里広域市町村圏組合</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="D30" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>471.5</v>
+        <v>438.3</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>492</v>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>+20.5</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>473.8</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>463</v>
+        <v>474.3</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>493.7</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>+55.3</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>509.2</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>521</v>
-      </c>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>+158.0</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>構成2町。当連合と同じく町村のみで構成する</t>
-        </is>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>557</v>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>+159.7</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>島原地域広域市町村圏組合</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>長崎県</t>
+          <t>日高中部広域連合</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>583</v>
+        <v>411.5</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>488.7</v>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>-94.3</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>488.4</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>480</v>
+        <v>471.5</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>+80.5</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>473.8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>505</v>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>+154.7</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr"/>
+        <v>463</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>521</v>
+      </c>
+      <c r="M31" s="13" t="inlineStr">
+        <is>
+          <t>+158.0</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>構成2町。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>砺波地方介護保険組合</t>
+          <t>島原地域広域市町村圏組合</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>富山県</t>
+          <t>長崎県</t>
         </is>
       </c>
       <c r="D32" s="13" t="n">
@@ -12505,44 +12585,47 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>512.3</v>
+        <v>603.7</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>481.7</v>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>-30.7</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>482.3</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>475</v>
+        <v>583</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>488.7</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>-115.0</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>488.4</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>488</v>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>+147.7</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr"/>
+        <v>480</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>505</v>
+      </c>
+      <c r="M32" s="13" t="inlineStr">
+        <is>
+          <t>+154.7</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>南部箕蚊屋広域連合</t>
+          <t>砺波地方介護保険組合</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>鳥取県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="D33" s="13" t="n">
@@ -12550,203 +12633,215 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>441.7</v>
+        <v>525.3</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>456.7</v>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>458.6</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>451</v>
+        <v>512.3</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>481.7</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>-43.7</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>482.3</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>464</v>
-      </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>+122.7</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr"/>
+        <v>475</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>488</v>
+      </c>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>+147.7</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>北アルプス広域連合</t>
+          <t>南部箕蚊屋広域連合</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>428</v>
+        <v>498.3</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>453.4</v>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>+25.4</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>431</v>
+        <v>441.7</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>456.7</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>-41.7</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>458.6</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>488</v>
-      </c>
-      <c r="L34" s="13" t="inlineStr">
-        <is>
-          <t>+119.4</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr"/>
+        <v>451</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>+122.7</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>後志広域連合</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="inlineStr">
-        <is>
-          <t>北海道</t>
+          <t>北アルプス広域連合</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>長野県</t>
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>421.1</v>
+        <v>391.4</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>436.4</v>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>+15.4</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>452.2</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>340</v>
+        <v>428</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>453.4</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>+62.0</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>442.1</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>535</v>
-      </c>
-      <c r="L35" s="13" t="inlineStr">
-        <is>
-          <t>+102.4</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>構成16町村。当連合と同じく町村のみで構成する</t>
-        </is>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>488</v>
+      </c>
+      <c r="M35" s="13" t="inlineStr">
+        <is>
+          <t>+119.4</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>新川地域介護保険・ケーブルテレビ事業組合</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>富山県</t>
+          <t>後志広域連合</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D36" s="13" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>412</v>
+        <v>399.9</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>434</v>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>+22.0</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>439.9</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>421</v>
+        <v>421.1</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>+36.6</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>452.2</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>458</v>
-      </c>
-      <c r="L36" s="13" t="inlineStr">
-        <is>
-          <t>+100.0</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr"/>
+        <v>340</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>535</v>
+      </c>
+      <c r="M36" s="13" t="inlineStr">
+        <is>
+          <t>+102.4</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>構成16町村。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>紀北広域連合</t>
+          <t>新川地域介護保険・ケーブルテレビ事業組合</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
@@ -12754,48 +12849,51 @@
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>459</v>
+        <v>409.7</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>430.5</v>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>-28.5</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>428.9</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>408</v>
+        <v>412</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>434</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>+24.3</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>439.9</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>453</v>
-      </c>
-      <c r="L37" s="13" t="inlineStr">
-        <is>
-          <t>+96.5</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr"/>
+        <v>421</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>458</v>
+      </c>
+      <c r="M37" s="13" t="inlineStr">
+        <is>
+          <t>+100.0</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>二戸地区広域行政事務組合</t>
+          <t>紀北広域連合</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>三重県</t>
         </is>
       </c>
       <c r="D38" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
@@ -12803,48 +12901,51 @@
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>447</v>
+        <v>382.5</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>426.2</v>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>-20.8</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>416</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>392</v>
+        <v>459</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>430.5</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>+48.0</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>428.9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>439</v>
-      </c>
-      <c r="L38" s="13" t="inlineStr">
-        <is>
-          <t>+92.2</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr"/>
+        <v>408</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>453</v>
+      </c>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>+96.5</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>諏訪広域連合</t>
+          <t>二戸地区広域行政事務組合</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
@@ -12852,48 +12953,51 @@
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>428.7</v>
+        <v>383.5</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>418.7</v>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>-10.0</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>429.7</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>367</v>
+        <v>447</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>426.2</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>+42.8</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>416</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>447</v>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>+84.7</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr"/>
+        <v>392</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>439</v>
+      </c>
+      <c r="M39" s="13" t="inlineStr">
+        <is>
+          <t>+92.2</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>東三河広域連合</t>
+          <t>諏訪広域連合</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
@@ -12901,146 +13005,155 @@
         </is>
       </c>
       <c r="F40" s="7" t="n">
-        <v>344.4</v>
+        <v>462</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>401.2</v>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>+56.9</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>414</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>327</v>
+        <v>428.7</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>-43.3</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>429.7</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>459</v>
-      </c>
-      <c r="L40" s="13" t="inlineStr">
-        <is>
-          <t>+67.2</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr"/>
+        <v>367</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>447</v>
+      </c>
+      <c r="M40" s="13" t="inlineStr">
+        <is>
+          <t>+84.7</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>揖斐広域連合</t>
+          <t>東三河広域連合</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F41" s="7" t="n">
-        <v>377.3</v>
+        <v>410.5</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>390</v>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>+12.7</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>391.6</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>321</v>
+        <v>344.4</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>401.2</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>-9.2</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>414</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>425</v>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>+56.0</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>459</v>
+      </c>
+      <c r="M41" s="13" t="inlineStr">
+        <is>
+          <t>+67.2</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>久慈広域連合</t>
+          <t>揖斐広域連合</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F42" s="7" t="n">
-        <v>357.2</v>
+        <v>393.3</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>375</v>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>+17.8</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>427.7</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>305</v>
+        <v>377.3</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>390</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>-3.3</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>391.6</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>475</v>
-      </c>
-      <c r="L42" s="13" t="inlineStr">
-        <is>
-          <t>+41.0</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr"/>
+        <v>321</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="M42" s="13" t="inlineStr">
+        <is>
+          <t>+56.0</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>みよし広域連合</t>
+          <t>久慈広域連合</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>徳島県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
@@ -13048,48 +13161,51 @@
         </is>
       </c>
       <c r="F43" s="7" t="n">
-        <v>342</v>
+        <v>368.5</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>374</v>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>+32.0</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>380.6</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>356</v>
+        <v>357.2</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>427.7</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="L43" s="13" t="inlineStr">
-        <is>
-          <t>+40.0</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="inlineStr"/>
+        <v>305</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>475</v>
+      </c>
+      <c r="M43" s="13" t="inlineStr">
+        <is>
+          <t>+41.0</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>もとす広域連合</t>
+          <t>みよし広域連合</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="D44" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
@@ -13097,44 +13213,47 @@
         </is>
       </c>
       <c r="F44" s="7" t="n">
-        <v>382.7</v>
+        <v>291</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>371.3</v>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>-11.3</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>309</v>
+        <v>342</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>374</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>+83.0</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>380.6</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>425</v>
-      </c>
-      <c r="L44" s="13" t="inlineStr">
-        <is>
-          <t>+37.3</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="inlineStr"/>
+        <v>356</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="M44" s="13" t="inlineStr">
+        <is>
+          <t>+40.0</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>盛岡北部行政事務組合</t>
+          <t>もとす広域連合</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="D45" s="13" t="n">
@@ -13146,427 +13265,453 @@
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>313</v>
+        <v>369</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>354</v>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>+41.0</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>356.9</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>345</v>
+        <v>382.7</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>+2.3</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>361.2</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>360</v>
-      </c>
-      <c r="L45" s="13" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr"/>
+        <v>309</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="M45" s="13" t="inlineStr">
+        <is>
+          <t>+37.3</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>中芸広域連合</t>
+          <t>盛岡北部行政事務組合</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>291.6</v>
+        <v>328.7</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>352</v>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>+60.4</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>351.7</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>348</v>
+        <v>313</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>354</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>+25.3</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>356.9</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>354</v>
-      </c>
-      <c r="L46" s="13" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="inlineStr"/>
+        <v>345</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="M46" s="13" t="inlineStr">
+        <is>
+          <t>+20.0</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>中芸広域連合</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>303.4</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>352</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>+48.6</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="M47" s="13" t="inlineStr">
+        <is>
+          <t>+18.0</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>沖縄県介護保険広域連合</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>沖縄県</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D48" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F48" s="7" t="n">
+        <v>276.9</v>
+      </c>
+      <c r="G48" s="7" t="n">
         <v>328.9</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="H48" s="7" t="n">
         <v>345.2</v>
       </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>+16.3</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="n">
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>+68.3</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="n">
         <v>381.4</v>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="K48" s="4" t="n">
         <v>191</v>
       </c>
-      <c r="K47" s="4" t="n">
+      <c r="L48" s="4" t="n">
         <v>495</v>
       </c>
-      <c r="L47" s="13" t="inlineStr">
+      <c r="M48" s="13" t="inlineStr">
         <is>
           <t>+11.2</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="28" t="n">
+      <c r="N48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="B48" s="29" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>大雪地区広域連合</t>
         </is>
       </c>
-      <c r="C48" s="28" t="inlineStr">
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="D48" s="28" t="n">
+      <c r="D49" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E49" s="28" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F48" s="11" t="n">
+      <c r="F49" s="11" t="n">
+        <v>332</v>
+      </c>
+      <c r="G49" s="11" t="n">
         <v>335.3</v>
       </c>
-      <c r="G48" s="21" t="n">
+      <c r="H49" s="21" t="n">
         <v>334</v>
       </c>
-      <c r="H48" s="28" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="n">
+      <c r="I49" s="28" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="n">
         <v>332.2</v>
       </c>
-      <c r="J48" s="8" t="n">
+      <c r="K49" s="8" t="n">
         <v>308</v>
       </c>
-      <c r="K48" s="8" t="n">
+      <c r="L49" s="8" t="n">
         <v>379</v>
       </c>
-      <c r="L48" s="28" t="inlineStr">
+      <c r="M49" s="28" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr">
-        <is>
-          <t>当連合。令和7年度から横ばいで、団体の平均が上がる中で位置が下がった</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>一関地区広域行政組合</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>岩手県</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>342</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>315.5</v>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>-26.5</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>316.8</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>314</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>317</v>
-      </c>
-      <c r="L49" s="13" t="inlineStr">
-        <is>
-          <t>-18.5</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>当連合。3か年ほぼ横ばいで、団体の平均が上がる中で位置が下がった</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>一関地区広域行政組合</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>342</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>-30.0</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>314</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="M50" s="13" t="inlineStr">
+        <is>
+          <t>-18.5</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>邑智郡総合事務組合</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>島根県</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D51" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F51" s="7" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="G51" s="7" t="n">
         <v>328.3</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="H51" s="7" t="n">
         <v>291.3</v>
       </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>-37.0</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="n">
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>-60.3</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="n">
         <v>268.9</v>
       </c>
-      <c r="J50" s="4" t="n">
+      <c r="K51" s="4" t="n">
         <v>231</v>
       </c>
-      <c r="K50" s="4" t="n">
+      <c r="L51" s="4" t="n">
         <v>337</v>
       </c>
-      <c r="L50" s="13" t="inlineStr">
+      <c r="M51" s="13" t="inlineStr">
         <is>
           <t>-42.7</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>【読み取り】当連合は38団体中36位です。38団体の平均は令和7年度450.7点から令和8年度466.9点へ+16.1点上がっているのに対し、当連合は335.3点から334.0点へ-1.3点で、団体の側でも同じ傾きの差が出ています。構成市町村の最低は308点・最高は379点で、区域内の開きは71点です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="56" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>【読み取り】当連合は38団体中36位です（令和6年度は34位）。38団体の平均は令和6年度443.4点→令和7年度450.7点→令和8年度466.9点と+23.5点上がっているのに対し、当連合は332.0点→335.3点→334.0点で+2.0点にとどまり、団体の側でも同じ傾きの差が出ています。3か年の伸びは38団体中27位です（下がった団体が11件あります）。構成市町村の最低は308点・最高は379点で、区域内の開きは71点です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>③ 同様の構成（町村のみで構成する団体）との比較</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>団体</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>都道府県</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>構成</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>市を含む</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>R6平均</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>R7平均</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>R8平均</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>R7→R8</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>R6→R8</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>加重平均</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>最低</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr">
         <is>
           <t>当連合との差</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="N55" s="3" t="inlineStr">
         <is>
           <t>見方</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>安八郡広域連合</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>岐阜県</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>498.7</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>575.3</v>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>+76.7</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="n">
-        <v>574.1</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>581</v>
-      </c>
-      <c r="L55" s="13" t="inlineStr">
-        <is>
-          <t>+241.3</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="inlineStr"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>木曽広域連合</t>
+          <t>安八郡広域連合</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>長野県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="D56" s="13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
@@ -13574,48 +13719,51 @@
         </is>
       </c>
       <c r="F56" s="7" t="n">
-        <v>518.8</v>
+        <v>487.7</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>535.8</v>
-      </c>
-      <c r="H56" s="13" t="inlineStr">
-        <is>
-          <t>+17.0</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="n">
-        <v>526.7</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>494</v>
+        <v>498.7</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>575.3</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>+87.7</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>574.1</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>568</v>
       </c>
-      <c r="L56" s="13" t="inlineStr">
-        <is>
-          <t>+201.8</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="n">
+        <v>581</v>
+      </c>
+      <c r="M56" s="13" t="inlineStr">
+        <is>
+          <t>+241.3</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>隠岐広域連合</t>
+          <t>木曽広域連合</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>島根県</t>
+          <t>長野県</t>
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
@@ -13623,97 +13771,103 @@
         </is>
       </c>
       <c r="F57" s="7" t="n">
-        <v>451.5</v>
+        <v>452</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>+69.2</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="n">
-        <v>498.2</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>486</v>
+        <v>518.8</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>+83.8</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>526.7</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>549</v>
-      </c>
-      <c r="L57" s="13" t="inlineStr">
-        <is>
-          <t>+186.8</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="inlineStr"/>
+        <v>494</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="M57" s="13" t="inlineStr">
+        <is>
+          <t>+201.8</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>隠岐広域連合</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>中新川広域行政事務組合</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>富山県</t>
-        </is>
-      </c>
-      <c r="D58" s="13" t="n">
-        <v>3</v>
-      </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
       <c r="F58" s="7" t="n">
-        <v>494</v>
+        <v>488.8</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>497.7</v>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="n">
-        <v>475.8</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>463</v>
+        <v>451.5</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>520.8</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>+32.0</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>498.2</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>545</v>
-      </c>
-      <c r="L58" s="13" t="inlineStr">
-        <is>
-          <t>+163.7</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="inlineStr"/>
+        <v>486</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>549</v>
+      </c>
+      <c r="M58" s="13" t="inlineStr">
+        <is>
+          <t>+186.8</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>日高中部広域連合</t>
+          <t>中新川広域行政事務組合</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>富山県</t>
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
@@ -13721,52 +13875,51 @@
         </is>
       </c>
       <c r="F59" s="7" t="n">
-        <v>471.5</v>
+        <v>539</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>492</v>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>+20.5</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="n">
-        <v>473.8</v>
-      </c>
-      <c r="J59" s="4" t="n">
+        <v>494</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>497.7</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>-41.3</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>475.8</v>
+      </c>
+      <c r="K59" s="4" t="n">
         <v>463</v>
       </c>
-      <c r="K59" s="4" t="n">
-        <v>521</v>
-      </c>
-      <c r="L59" s="13" t="inlineStr">
-        <is>
-          <t>+158.0</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
-        <is>
-          <t>構成2町。当連合と同じく町村のみで構成する</t>
-        </is>
-      </c>
+      <c r="L59" s="4" t="n">
+        <v>545</v>
+      </c>
+      <c r="M59" s="13" t="inlineStr">
+        <is>
+          <t>+163.7</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>南部箕蚊屋広域連合</t>
+          <t>日高中部広域連合</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>鳥取県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D60" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
@@ -13774,48 +13927,55 @@
         </is>
       </c>
       <c r="F60" s="7" t="n">
-        <v>441.7</v>
+        <v>411.5</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>456.7</v>
-      </c>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="n">
-        <v>458.6</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>451</v>
+        <v>471.5</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>+80.5</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>473.8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>464</v>
-      </c>
-      <c r="L60" s="13" t="inlineStr">
-        <is>
-          <t>+122.7</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="inlineStr"/>
+        <v>463</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>521</v>
+      </c>
+      <c r="M60" s="13" t="inlineStr">
+        <is>
+          <t>+158.0</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>構成2町。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>後志広域連合</t>
+          <t>南部箕蚊屋広域連合</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
@@ -13823,52 +13983,51 @@
         </is>
       </c>
       <c r="F61" s="7" t="n">
-        <v>421.1</v>
+        <v>498.3</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>436.4</v>
-      </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>+15.4</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="n">
-        <v>452.2</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>340</v>
+        <v>441.7</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>456.7</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>-41.7</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>458.6</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>535</v>
-      </c>
-      <c r="L61" s="13" t="inlineStr">
-        <is>
-          <t>+102.4</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="inlineStr">
-        <is>
-          <t>構成16町村。当連合と同じく町村のみで構成する</t>
-        </is>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="M61" s="13" t="inlineStr">
+        <is>
+          <t>+122.7</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>揖斐広域連合</t>
+          <t>後志広域連合</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>岐阜県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D62" s="13" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
@@ -13876,324 +14035,344 @@
         </is>
       </c>
       <c r="F62" s="7" t="n">
-        <v>377.3</v>
+        <v>399.9</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>390</v>
-      </c>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>+12.7</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="n">
-        <v>391.6</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>321</v>
+        <v>421.1</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>436.4</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>+36.6</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>452.2</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>425</v>
-      </c>
-      <c r="L62" s="13" t="inlineStr">
-        <is>
-          <t>+56.0</t>
-        </is>
-      </c>
-      <c r="M62" s="4" t="inlineStr"/>
+        <v>340</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>535</v>
+      </c>
+      <c r="M62" s="13" t="inlineStr">
+        <is>
+          <t>+102.4</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>構成16町村。当連合と同じく町村のみで構成する</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>揖斐広域連合</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>390</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>-3.3</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>321</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="M63" s="13" t="inlineStr">
+        <is>
+          <t>+56.0</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>中芸広域連合</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>高知県</t>
         </is>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D64" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F64" s="7" t="n">
+        <v>303.4</v>
+      </c>
+      <c r="G64" s="7" t="n">
         <v>291.6</v>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="H64" s="7" t="n">
         <v>352</v>
       </c>
-      <c r="H63" s="13" t="inlineStr">
-        <is>
-          <t>+60.4</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="n">
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>+48.6</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="n">
         <v>351.7</v>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="K64" s="4" t="n">
         <v>348</v>
       </c>
-      <c r="K63" s="4" t="n">
+      <c r="L64" s="4" t="n">
         <v>354</v>
       </c>
-      <c r="L63" s="13" t="inlineStr">
+      <c r="M64" s="13" t="inlineStr">
         <is>
           <t>+18.0</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="28" t="n">
+      <c r="N64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>大雪地区広域連合</t>
         </is>
       </c>
-      <c r="C64" s="28" t="inlineStr">
+      <c r="C65" s="28" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="D64" s="28" t="n">
+      <c r="D65" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="E64" s="28" t="inlineStr">
+      <c r="E65" s="28" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F64" s="11" t="n">
+      <c r="F65" s="11" t="n">
+        <v>332</v>
+      </c>
+      <c r="G65" s="11" t="n">
         <v>335.3</v>
       </c>
-      <c r="G64" s="21" t="n">
+      <c r="H65" s="21" t="n">
         <v>334</v>
       </c>
-      <c r="H64" s="28" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="n">
+      <c r="I65" s="28" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="n">
         <v>332.2</v>
       </c>
-      <c r="J64" s="8" t="n">
+      <c r="K65" s="8" t="n">
         <v>308</v>
       </c>
-      <c r="K64" s="8" t="n">
+      <c r="L65" s="8" t="n">
         <v>379</v>
       </c>
-      <c r="L64" s="28" t="inlineStr">
+      <c r="M65" s="28" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M64" s="8" t="inlineStr">
-        <is>
-          <t>当連合。令和7年度から横ばいで、団体の平均が上がる中で位置が下がった</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="13" t="n">
+      <c r="N65" s="8" t="inlineStr">
+        <is>
+          <t>当連合。3か年ほぼ横ばいで、団体の平均が上がる中で位置が下がった</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>邑智郡総合事務組合</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>島根県</t>
         </is>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D66" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F66" s="7" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="G66" s="7" t="n">
         <v>328.3</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="H66" s="7" t="n">
         <v>291.3</v>
       </c>
-      <c r="H65" s="13" t="inlineStr">
-        <is>
-          <t>-37.0</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="n">
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>-60.3</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="n">
         <v>268.9</v>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="K66" s="4" t="n">
         <v>231</v>
       </c>
-      <c r="K65" s="4" t="n">
+      <c r="L66" s="4" t="n">
         <v>337</v>
       </c>
-      <c r="L65" s="13" t="inlineStr">
+      <c r="M66" s="13" t="inlineStr">
         <is>
           <t>-42.7</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66" ht="44" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>【読み取り】市を含まず町村のみで構成する団体は11団体あり、当連合はその中で10位です。11団体の平均は443.8点で、当連合は109.8点低くなっています。令和7年度から下がったのは2団体だけです。町村のみで構成することが低位の理由にはなっていません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="N66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>【読み取り】市を含まず町村のみで構成する団体は11団体あり、当連合はその中で10位です。11団体の平均は443.8点で、当連合は109.8点低くなっています。令和6年度から下がったのは4団体だけです。町村のみで構成することが低位の理由にはなっていません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>④ 北海道内の団体</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>団体</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>都道府県</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>構成</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>市を含む</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>R6平均</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>R7平均</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>R8平均</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>R7→R8</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>R6→R8</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>加重平均</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>最低</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr">
         <is>
           <t>当連合との差</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
+      <c r="N70" s="3" t="inlineStr">
         <is>
           <t>構成市町村</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>空知中部広域連合</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E70" s="13" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>542.5</v>
-      </c>
-      <c r="G70" s="7" t="n">
-        <v>563.3</v>
-      </c>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>+20.8</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="n">
-        <v>566.2</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>528</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>615</v>
-      </c>
-      <c r="L70" s="13" t="inlineStr">
-        <is>
-          <t>+229.3</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="inlineStr">
-        <is>
-          <t>歌志内市・奈井江町・上砂川町・浦臼町・新十津川町・雨竜町</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>日高中部広域連合</t>
+          <t>空知中部広域連合</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -14202,223 +14381,266 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F71" s="7" t="n">
-        <v>471.5</v>
+        <v>545.5</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>492</v>
-      </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>+20.5</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n">
-        <v>473.8</v>
-      </c>
-      <c r="J71" s="4" t="n">
-        <v>463</v>
+        <v>542.5</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>563.3</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>+17.8</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>566.2</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>521</v>
-      </c>
-      <c r="L71" s="13" t="inlineStr">
-        <is>
-          <t>+158.0</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="inlineStr">
-        <is>
-          <t>新冠町・新ひだか町</t>
+        <v>528</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>615</v>
+      </c>
+      <c r="M71" s="13" t="inlineStr">
+        <is>
+          <t>+229.3</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>歌志内市・奈井江町・上砂川町・浦臼町・新十津川町・雨竜町</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>日高中部広域連合</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>411.5</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>471.5</v>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>+80.5</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>463</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>521</v>
+      </c>
+      <c r="M72" s="13" t="inlineStr">
+        <is>
+          <t>+158.0</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>新冠町・新ひだか町</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>後志広域連合</t>
         </is>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D73" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="E72" s="13" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="F73" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="G73" s="7" t="n">
         <v>421.1</v>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="H73" s="7" t="n">
         <v>436.4</v>
       </c>
-      <c r="H72" s="13" t="inlineStr">
-        <is>
-          <t>+15.4</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="n">
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>+36.6</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="n">
         <v>452.2</v>
       </c>
-      <c r="J72" s="4" t="n">
+      <c r="K73" s="4" t="n">
         <v>340</v>
       </c>
-      <c r="K72" s="4" t="n">
+      <c r="L73" s="4" t="n">
         <v>535</v>
       </c>
-      <c r="L72" s="13" t="inlineStr">
+      <c r="M73" s="13" t="inlineStr">
         <is>
           <t>+102.4</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>島牧村・黒松内町・蘭越町・ニセコ町・真狩村・留寿都村・喜茂別町・京極町・倶知安町・共和町・泊村・神恵内村・積丹町・古平町・仁木町・赤井川村</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="28" t="n">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>大雪地区広域連合</t>
         </is>
       </c>
-      <c r="C73" s="28" t="inlineStr">
+      <c r="C74" s="28" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="D73" s="28" t="n">
+      <c r="D74" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="E73" s="28" t="inlineStr">
+      <c r="E74" s="28" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F73" s="11" t="n">
+      <c r="F74" s="11" t="n">
+        <v>332</v>
+      </c>
+      <c r="G74" s="11" t="n">
         <v>335.3</v>
       </c>
-      <c r="G73" s="21" t="n">
+      <c r="H74" s="21" t="n">
         <v>334</v>
       </c>
-      <c r="H73" s="28" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="n">
+      <c r="I74" s="28" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="n">
         <v>332.2</v>
       </c>
-      <c r="J73" s="8" t="n">
+      <c r="K74" s="8" t="n">
         <v>308</v>
       </c>
-      <c r="K73" s="8" t="n">
+      <c r="L74" s="8" t="n">
         <v>379</v>
       </c>
-      <c r="L73" s="28" t="inlineStr">
+      <c r="M74" s="28" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M73" s="8" t="inlineStr">
+      <c r="N74" s="8" t="inlineStr">
         <is>
           <t>東川町・美瑛町・東神楽町</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="36" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>【読み取り】北海道内の団体は4件で、当連合は最も低い水準です。最も高い空知中部広域連合とは229.3点の差があります。後志広域連合・日高中部広域連合は当連合と同じく町村のみで構成しますが、いずれも当連合を上回っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>【読み取り】北海道内の団体は4件で、当連合は3か年とも最も低い水準です。最も高い空知中部広域連合とは令和8年度で229.3点の差があります。後志広域連合・日高中部広域連合は当連合と同じく町村のみで構成しますが、いずれも当連合を上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>⑤ なお確かめられていないこと</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>事項</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="inlineStr"/>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
-      <c r="K77" s="3" t="inlineStr"/>
-      <c r="L77" s="3" t="inlineStr"/>
-      <c r="M77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78" ht="40" customHeight="1">
-      <c r="A78" s="24" t="inlineStr">
-        <is>
-          <t>令和6年度の団体別の値</t>
-        </is>
-      </c>
-      <c r="B78" s="25" t="inlineStr">
-        <is>
-          <t>受領した原本は令和8年度の集計で、令和7年度の合計得点は併載されているが令和6年度はない。3か年の推移を団体別に示すには令和6年度の原本を要する（確認事項No.168）。</t>
-        </is>
-      </c>
-      <c r="C78" s="26" t="n"/>
-      <c r="D78" s="26" t="n"/>
-      <c r="E78" s="26" t="n"/>
-      <c r="F78" s="26" t="n"/>
-      <c r="G78" s="26" t="n"/>
-      <c r="H78" s="26" t="n"/>
-      <c r="I78" s="26" t="n"/>
-      <c r="J78" s="26" t="n"/>
-      <c r="K78" s="26" t="n"/>
-      <c r="L78" s="26" t="n"/>
-      <c r="M78" s="26" t="n"/>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr"/>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>団体名を成果品に掲げること</t>
+          <t>令和7年度の内訳</t>
         </is>
       </c>
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>本シートの団体名は公表されている全国集計の行の名称であり、他団体が策定した計画その他の資料によるものではない。成果品に団体名を掲げてよいかをご確認いただきたい（確認事項No.168）。</t>
+          <t>令和7年度は合計得点と順位のみである（令和8年度の集計に併載されている）。推進と支援の別、目標別・大項目別の内訳は令和7年度の原本を要する。3か年の合計得点の比較はできている。</t>
         </is>
       </c>
       <c r="C79" s="26" t="n"/>
@@ -14432,16 +14654,17 @@
       <c r="K79" s="26" t="n"/>
       <c r="L79" s="26" t="n"/>
       <c r="M79" s="26" t="n"/>
+      <c r="N79" s="26" t="n"/>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>得点0の理由</t>
+          <t>令和6年度にあって令和8年度にない団体が2件ある</t>
         </is>
       </c>
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>他団体についても、得点0が「取組がない」のか「要件を満たさない」のかは公表資料から判別できない。得点の差をそのまま取組の差と読まない（確認事項No.6）。</t>
+          <t>本荘由利広域市町村圏組合（秋田県）とくすのき広域連合（大阪府）は令和6年度の集計にあり令和8年度の集計にない。3か年を通して比べられるのは38団体である。38団体の構成市町村は令和6年度と令和8年度で完全に一致する。</t>
         </is>
       </c>
       <c r="C80" s="26" t="n"/>
@@ -14455,16 +14678,17 @@
       <c r="K80" s="26" t="n"/>
       <c r="L80" s="26" t="n"/>
       <c r="M80" s="26" t="n"/>
+      <c r="N80" s="26" t="n"/>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>平均の置き方</t>
+          <t>団体名を成果品に掲げること</t>
         </is>
       </c>
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>本シートは構成市町村の単純平均を主とし、第1号被保険者数で加重した値を併せて掲げた。構成市町村の数と規模が団体により大きく異なるため、どちらを用いるかで順位が入れ替わる団体がある。</t>
+          <t>本シートの団体名は公表されている全国集計の行の名称であり、他団体が策定した計画その他の資料によるものではない。成果品に団体名を掲げてよいかをご確認いただきたい（確認事項No.168）。</t>
         </is>
       </c>
       <c r="C81" s="26" t="n"/>
@@ -14478,26 +14702,77 @@
       <c r="K81" s="26" t="n"/>
       <c r="L81" s="26" t="n"/>
       <c r="M81" s="26" t="n"/>
+      <c r="N81" s="26" t="n"/>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>得点0の理由</t>
+        </is>
+      </c>
+      <c r="B82" s="25" t="inlineStr">
+        <is>
+          <t>他団体についても、得点0が「取組がない」のか「要件を満たさない」のかは公表資料から判別できない。得点の差をそのまま取組の差と読まない（確認事項No.6）。</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="n"/>
+      <c r="D82" s="26" t="n"/>
+      <c r="E82" s="26" t="n"/>
+      <c r="F82" s="26" t="n"/>
+      <c r="G82" s="26" t="n"/>
+      <c r="H82" s="26" t="n"/>
+      <c r="I82" s="26" t="n"/>
+      <c r="J82" s="26" t="n"/>
+      <c r="K82" s="26" t="n"/>
+      <c r="L82" s="26" t="n"/>
+      <c r="M82" s="26" t="n"/>
+      <c r="N82" s="26" t="n"/>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>平均の置き方</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>本シートは構成市町村の単純平均を主とし、第1号被保険者数で加重した値を併せて掲げた。構成市町村の数と規模が団体により大きく異なるため、どちらを用いるかで順位が入れ替わる団体がある。</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="n"/>
+      <c r="D83" s="26" t="n"/>
+      <c r="E83" s="26" t="n"/>
+      <c r="F83" s="26" t="n"/>
+      <c r="G83" s="26" t="n"/>
+      <c r="H83" s="26" t="n"/>
+      <c r="I83" s="26" t="n"/>
+      <c r="J83" s="26" t="n"/>
+      <c r="K83" s="26" t="n"/>
+      <c r="L83" s="26" t="n"/>
+      <c r="M83" s="26" t="n"/>
+      <c r="N83" s="26" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B6:M6"/>
-    <mergeCell ref="A76:M76"/>
-    <mergeCell ref="A68:M68"/>
-    <mergeCell ref="A66:M66"/>
-    <mergeCell ref="B78:M78"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="B81:M81"/>
-    <mergeCell ref="B80:M80"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="B8:M8"/>
-    <mergeCell ref="A53:M53"/>
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B79:M79"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
+  <mergeCells count="19">
+    <mergeCell ref="A67:N67"/>
+    <mergeCell ref="A77:N77"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="B83:N83"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B80:N80"/>
+    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="B79:N79"/>
+    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="B7:N7"/>
+    <mergeCell ref="A75:N75"/>
+    <mergeCell ref="B81:N81"/>
+    <mergeCell ref="A12:N12"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="B8:N8"/>
+    <mergeCell ref="A52:N52"/>
+    <mergeCell ref="B82:N82"/>
+    <mergeCell ref="B10:N10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,6 +229,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1960,7 +1966,7 @@
       <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>可</t>
         </is>
@@ -1986,7 +1992,7 @@
       <c r="J25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>条件付き</t>
         </is>
@@ -2012,7 +2018,7 @@
       <c r="J26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="38" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>現時点では不可</t>
         </is>
@@ -3458,7 +3464,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>同様の構成の団体との比較（団体名の掲載と令和7年度の内訳）</t>
+          <t>同様の構成の団体との比較と団体名の扱い</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3466,9 +3472,9 @@
           <t>発注者</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>一部確認済み</t>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>解決</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -3546,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4042,7 +4048,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>令和6年度のみの団体2件</t>
+          <t>令和8年度の集計にない団体2件</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -4053,18 +4059,14 @@
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>当連合の令和6年度の平均が3町平均と一致すること</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>332.0</t>
-        </is>
-      </c>
+          <t>推進と支援の和が推進・支援合計と一致すること（3か年・205市町村）</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
       <c r="D30" s="14" t="inlineStr">
         <is>
           <t>適合</t>
@@ -4073,18 +4075,14 @@
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>当連合の平均が3町平均と一致すること</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>334.0</t>
-        </is>
-      </c>
+          <t>当連合の構成市町村の推進・支援が収録値と一致すること（3か年）</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
       <c r="D31" s="14" t="inlineStr">
         <is>
           <t>適合</t>
@@ -4093,16 +4091,16 @@
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>団体の順位づけに重複・欠落がないこと</t>
+          <t>当連合の令和6年度の平均が3町平均と一致すること</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>全38団体・町村のみ11団体・北海道4団体</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -4113,16 +4111,16 @@
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>19施策のすべてに第10期の基本目標の対照があること</t>
+          <t>当連合の平均が3町平均と一致すること</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>対照のないものなし</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -4133,16 +4131,16 @@
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>介護給付費の適正化が第10期の基本目標5に移ることを反映していること</t>
+          <t>団体の順位づけに重複・欠落がないこと</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>施策4-3→第5章 基本目標5</t>
+          <t>全38団体・町村のみ11団体・北海道4団体</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -4153,15 +4151,75 @@
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>19施策のすべてに第10期の基本目標の対照があること</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>対照のないものなし</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>介護給付費の適正化が第10期の基本目標5に移ることを反映していること</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>施策4-3→第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>計画素案に他の団体の名が現れないこと（協議用の資料には掲げ、計画素案には掲げない。当連合は除く）</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>見つかったものなし</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>受託者の内部の仕組みの語を本文に書いていないこと</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -11351,7 +11409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14600,178 +14658,413 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>⑤ なお確かめられていないこと</t>
+          <t>⑤ 推進と支援の別（構成市町村の平均）</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>事項</t>
+          <t>団体</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr"/>
-      <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" s="3" t="inlineStr"/>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+          <t>推進R6</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>推進R7</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>推進R8</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>推進R6→R8</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>支援R6</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>支援R7</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>支援R8</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>支援R6→R8</t>
+        </is>
+      </c>
       <c r="K78" s="3" t="inlineStr"/>
       <c r="L78" s="3" t="inlineStr"/>
       <c r="M78" s="3" t="inlineStr"/>
-      <c r="N78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79" ht="40" customHeight="1">
-      <c r="A79" s="24" t="inlineStr">
-        <is>
-          <t>令和7年度の内訳</t>
-        </is>
-      </c>
-      <c r="B79" s="25" t="inlineStr">
-        <is>
-          <t>令和7年度は合計得点と順位のみである（令和8年度の集計に併載されている）。推進と支援の別、目標別・大項目別の内訳は令和7年度の原本を要する。3か年の合計得点の比較はできている。</t>
-        </is>
-      </c>
-      <c r="C79" s="26" t="n"/>
-      <c r="D79" s="26" t="n"/>
-      <c r="E79" s="26" t="n"/>
-      <c r="F79" s="26" t="n"/>
-      <c r="G79" s="26" t="n"/>
-      <c r="H79" s="26" t="n"/>
-      <c r="I79" s="26" t="n"/>
-      <c r="J79" s="26" t="n"/>
-      <c r="K79" s="26" t="n"/>
-      <c r="L79" s="26" t="n"/>
-      <c r="M79" s="26" t="n"/>
-      <c r="N79" s="26" t="n"/>
-    </row>
-    <row r="80" ht="40" customHeight="1">
-      <c r="A80" s="24" t="inlineStr">
-        <is>
-          <t>令和6年度にあって令和8年度にない団体が2件ある</t>
-        </is>
-      </c>
-      <c r="B80" s="25" t="inlineStr">
-        <is>
-          <t>本荘由利広域市町村圏組合（秋田県）とくすのき広域連合（大阪府）は令和6年度の集計にあり令和8年度の集計にない。3か年を通して比べられるのは38団体である。38団体の構成市町村は令和6年度と令和8年度で完全に一致する。</t>
-        </is>
-      </c>
-      <c r="C80" s="26" t="n"/>
-      <c r="D80" s="26" t="n"/>
-      <c r="E80" s="26" t="n"/>
-      <c r="F80" s="26" t="n"/>
-      <c r="G80" s="26" t="n"/>
-      <c r="H80" s="26" t="n"/>
-      <c r="I80" s="26" t="n"/>
-      <c r="J80" s="26" t="n"/>
-      <c r="K80" s="26" t="n"/>
-      <c r="L80" s="26" t="n"/>
-      <c r="M80" s="26" t="n"/>
-      <c r="N80" s="26" t="n"/>
-    </row>
-    <row r="81" ht="40" customHeight="1">
-      <c r="A81" s="24" t="inlineStr">
-        <is>
-          <t>団体名を成果品に掲げること</t>
-        </is>
-      </c>
-      <c r="B81" s="25" t="inlineStr">
-        <is>
-          <t>本シートの団体名は公表されている全国集計の行の名称であり、他団体が策定した計画その他の資料によるものではない。成果品に団体名を掲げてよいかをご確認いただきたい（確認事項No.168）。</t>
-        </is>
-      </c>
-      <c r="C81" s="26" t="n"/>
-      <c r="D81" s="26" t="n"/>
-      <c r="E81" s="26" t="n"/>
-      <c r="F81" s="26" t="n"/>
-      <c r="G81" s="26" t="n"/>
-      <c r="H81" s="26" t="n"/>
-      <c r="I81" s="26" t="n"/>
-      <c r="J81" s="26" t="n"/>
-      <c r="K81" s="26" t="n"/>
-      <c r="L81" s="26" t="n"/>
-      <c r="M81" s="26" t="n"/>
-      <c r="N81" s="26" t="n"/>
-    </row>
-    <row r="82" ht="40" customHeight="1">
-      <c r="A82" s="24" t="inlineStr">
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="29" t="inlineStr">
+        <is>
+          <t>当連合</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="C79" s="30" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="D79" s="30" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="E79" s="30" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="F79" s="28" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
+      <c r="G79" s="30" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="H79" s="30" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="I79" s="30" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="J79" s="28" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="8" t="inlineStr"/>
+      <c r="M79" s="8" t="inlineStr"/>
+      <c r="N79" s="8" t="inlineStr">
+        <is>
+          <t>推進は上がったが支援が下がっている</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>38団体の平均</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C80" s="31" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="D80" s="31" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="E80" s="31" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>+18.6</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="n">
+        <v>222.8</v>
+      </c>
+      <c r="H80" s="31" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="I80" s="31" t="n">
+        <v>227.7</v>
+      </c>
+      <c r="J80" s="13" t="inlineStr">
+        <is>
+          <t>+4.9</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>推進・支援とも上がっている</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>町村のみ11団体の平均</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>+19.1</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>213.6</v>
+      </c>
+      <c r="H81" s="31" t="n">
+        <v>205.4</v>
+      </c>
+      <c r="I81" s="31" t="n">
+        <v>215</v>
+      </c>
+      <c r="J81" s="13" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr"/>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>北海道内4団体の平均</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>224</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>+17.3</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="H82" s="31" t="n">
+        <v>218.6</v>
+      </c>
+      <c r="I82" s="31" t="n">
+        <v>228</v>
+      </c>
+      <c r="J82" s="13" t="inlineStr">
+        <is>
+          <t>+17.0</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>【読み取り】当連合は推進が164.7→172.7点（+8.0）、支援が167.3→161.3点（-6.0）です。38団体の平均は推進+18.6点・支援+4.9点であり、推進・支援のどちらでも差が開いている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>⑥ なお確かめられていないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>令和8年度の集計にない団体が2件ある</t>
+        </is>
+      </c>
+      <c r="B87" s="25" t="inlineStr">
+        <is>
+          <t>本荘由利広域市町村圏組合（秋田県）は令和6・7年度に、くすのき広域連合（大阪府）は令和6年度に現れ、令和8年度の集計にない。3か年を通して比べられるのは38団体である。38団体の構成市町村は令和6・7・8年度で完全に一致する。</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="n"/>
+      <c r="D87" s="26" t="n"/>
+      <c r="E87" s="26" t="n"/>
+      <c r="F87" s="26" t="n"/>
+      <c r="G87" s="26" t="n"/>
+      <c r="H87" s="26" t="n"/>
+      <c r="I87" s="26" t="n"/>
+      <c r="J87" s="26" t="n"/>
+      <c r="K87" s="26" t="n"/>
+      <c r="L87" s="26" t="n"/>
+      <c r="M87" s="26" t="n"/>
+      <c r="N87" s="26" t="n"/>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>団体名の扱い</t>
+        </is>
+      </c>
+      <c r="B88" s="25" t="inlineStr">
+        <is>
+          <t>本シートの団体名は公表されている全国集計の行の名称であり、他団体が策定した計画その他の資料によるものではない。協議用の資料には団体名を掲げ、計画素案には掲げない扱いとする（令和8年9月29日 ご指示）。</t>
+        </is>
+      </c>
+      <c r="C88" s="26" t="n"/>
+      <c r="D88" s="26" t="n"/>
+      <c r="E88" s="26" t="n"/>
+      <c r="F88" s="26" t="n"/>
+      <c r="G88" s="26" t="n"/>
+      <c r="H88" s="26" t="n"/>
+      <c r="I88" s="26" t="n"/>
+      <c r="J88" s="26" t="n"/>
+      <c r="K88" s="26" t="n"/>
+      <c r="L88" s="26" t="n"/>
+      <c r="M88" s="26" t="n"/>
+      <c r="N88" s="26" t="n"/>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>得点0の理由</t>
         </is>
       </c>
-      <c r="B82" s="25" t="inlineStr">
+      <c r="B89" s="25" t="inlineStr">
         <is>
           <t>他団体についても、得点0が「取組がない」のか「要件を満たさない」のかは公表資料から判別できない。得点の差をそのまま取組の差と読まない（確認事項No.6）。</t>
         </is>
       </c>
-      <c r="C82" s="26" t="n"/>
-      <c r="D82" s="26" t="n"/>
-      <c r="E82" s="26" t="n"/>
-      <c r="F82" s="26" t="n"/>
-      <c r="G82" s="26" t="n"/>
-      <c r="H82" s="26" t="n"/>
-      <c r="I82" s="26" t="n"/>
-      <c r="J82" s="26" t="n"/>
-      <c r="K82" s="26" t="n"/>
-      <c r="L82" s="26" t="n"/>
-      <c r="M82" s="26" t="n"/>
-      <c r="N82" s="26" t="n"/>
-    </row>
-    <row r="83" ht="40" customHeight="1">
-      <c r="A83" s="24" t="inlineStr">
+      <c r="C89" s="26" t="n"/>
+      <c r="D89" s="26" t="n"/>
+      <c r="E89" s="26" t="n"/>
+      <c r="F89" s="26" t="n"/>
+      <c r="G89" s="26" t="n"/>
+      <c r="H89" s="26" t="n"/>
+      <c r="I89" s="26" t="n"/>
+      <c r="J89" s="26" t="n"/>
+      <c r="K89" s="26" t="n"/>
+      <c r="L89" s="26" t="n"/>
+      <c r="M89" s="26" t="n"/>
+      <c r="N89" s="26" t="n"/>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
         <is>
           <t>平均の置き方</t>
         </is>
       </c>
-      <c r="B83" s="25" t="inlineStr">
+      <c r="B90" s="25" t="inlineStr">
         <is>
           <t>本シートは構成市町村の単純平均を主とし、第1号被保険者数で加重した値を併せて掲げた。構成市町村の数と規模が団体により大きく異なるため、どちらを用いるかで順位が入れ替わる団体がある。</t>
         </is>
       </c>
-      <c r="C83" s="26" t="n"/>
-      <c r="D83" s="26" t="n"/>
-      <c r="E83" s="26" t="n"/>
-      <c r="F83" s="26" t="n"/>
-      <c r="G83" s="26" t="n"/>
-      <c r="H83" s="26" t="n"/>
-      <c r="I83" s="26" t="n"/>
-      <c r="J83" s="26" t="n"/>
-      <c r="K83" s="26" t="n"/>
-      <c r="L83" s="26" t="n"/>
-      <c r="M83" s="26" t="n"/>
-      <c r="N83" s="26" t="n"/>
+      <c r="C90" s="26" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="26" t="n"/>
+      <c r="F90" s="26" t="n"/>
+      <c r="G90" s="26" t="n"/>
+      <c r="H90" s="26" t="n"/>
+      <c r="I90" s="26" t="n"/>
+      <c r="J90" s="26" t="n"/>
+      <c r="K90" s="26" t="n"/>
+      <c r="L90" s="26" t="n"/>
+      <c r="M90" s="26" t="n"/>
+      <c r="N90" s="26" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A67:N67"/>
     <mergeCell ref="A77:N77"/>
+    <mergeCell ref="A83:N83"/>
     <mergeCell ref="B9:N9"/>
-    <mergeCell ref="B83:N83"/>
     <mergeCell ref="B6:N6"/>
-    <mergeCell ref="B80:N80"/>
+    <mergeCell ref="B89:N89"/>
     <mergeCell ref="A69:N69"/>
-    <mergeCell ref="B79:N79"/>
     <mergeCell ref="A54:N54"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="A75:N75"/>
-    <mergeCell ref="B81:N81"/>
+    <mergeCell ref="B90:N90"/>
     <mergeCell ref="A12:N12"/>
     <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A85:N85"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="A52:N52"/>
-    <mergeCell ref="B82:N82"/>
+    <mergeCell ref="B88:N88"/>
+    <mergeCell ref="B87:N87"/>
     <mergeCell ref="B10:N10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15745,7 +16038,7 @@
       <c r="F26" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G26" s="30" t="n">
+      <c r="G26" s="32" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -15787,7 +16080,7 @@
       <c r="F27" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="30" t="n">
+      <c r="G27" s="32" t="n">
         <v>91.90000000000001</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -15829,7 +16122,7 @@
       <c r="F28" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G28" s="30" t="n">
+      <c r="G28" s="32" t="n">
         <v>88</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -15871,7 +16164,7 @@
       <c r="F29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="30" t="n">
+      <c r="G29" s="32" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -15913,7 +16206,7 @@
       <c r="F30" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G30" s="30" t="n">
+      <c r="G30" s="32" t="n">
         <v>85.3</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -15955,7 +16248,7 @@
       <c r="F31" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="30" t="n">
+      <c r="G31" s="32" t="n">
         <v>83.5</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -15997,7 +16290,7 @@
       <c r="F32" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G32" s="30" t="n">
+      <c r="G32" s="32" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -16039,7 +16332,7 @@
       <c r="F33" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G33" s="30" t="n">
+      <c r="G33" s="32" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -16081,7 +16374,7 @@
       <c r="F34" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G34" s="30" t="n">
+      <c r="G34" s="32" t="n">
         <v>80</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -16123,7 +16416,7 @@
       <c r="F35" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="30" t="n">
+      <c r="G35" s="32" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -16165,7 +16458,7 @@
       <c r="F36" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G36" s="30" t="n">
+      <c r="G36" s="32" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -16207,7 +16500,7 @@
       <c r="F37" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G37" s="30" t="n">
+      <c r="G37" s="32" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -16249,7 +16542,7 @@
       <c r="F38" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G38" s="30" t="n">
+      <c r="G38" s="32" t="n">
         <v>76.3</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -16291,7 +16584,7 @@
       <c r="F39" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="30" t="n">
+      <c r="G39" s="32" t="n">
         <v>75.8</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -16333,7 +16626,7 @@
       <c r="F40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="30" t="n">
+      <c r="G40" s="32" t="n">
         <v>71</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -16375,7 +16668,7 @@
       <c r="F41" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="30" t="n">
+      <c r="G41" s="32" t="n">
         <v>70.5</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -16417,7 +16710,7 @@
       <c r="F42" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="30" t="n">
+      <c r="G42" s="32" t="n">
         <v>70</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -16459,7 +16752,7 @@
       <c r="F43" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="30" t="n">
+      <c r="G43" s="32" t="n">
         <v>70</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -16501,7 +16794,7 @@
       <c r="F44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="30" t="n">
+      <c r="G44" s="32" t="n">
         <v>70</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -16543,7 +16836,7 @@
       <c r="F45" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="31" t="n">
+      <c r="G45" s="33" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -16585,7 +16878,7 @@
       <c r="F46" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G46" s="31" t="n">
+      <c r="G46" s="33" t="n">
         <v>64.5</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -16627,7 +16920,7 @@
       <c r="F47" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G47" s="31" t="n">
+      <c r="G47" s="33" t="n">
         <v>62.1</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -16669,7 +16962,7 @@
       <c r="F48" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G48" s="31" t="n">
+      <c r="G48" s="33" t="n">
         <v>61.3</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -16711,7 +17004,7 @@
       <c r="F49" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G49" s="31" t="n">
+      <c r="G49" s="33" t="n">
         <v>60.4</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -16753,7 +17046,7 @@
       <c r="F50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="31" t="n">
+      <c r="G50" s="33" t="n">
         <v>59</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
@@ -16795,7 +17088,7 @@
       <c r="F51" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="31" t="n">
+      <c r="G51" s="33" t="n">
         <v>58.2</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -16837,7 +17130,7 @@
       <c r="F52" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G52" s="31" t="n">
+      <c r="G52" s="33" t="n">
         <v>57.1</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -16879,7 +17172,7 @@
       <c r="F53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="31" t="n">
+      <c r="G53" s="33" t="n">
         <v>54.9</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -16921,7 +17214,7 @@
       <c r="F54" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="31" t="n">
+      <c r="G54" s="33" t="n">
         <v>53.4</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -16963,7 +17256,7 @@
       <c r="F55" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G55" s="31" t="n">
+      <c r="G55" s="33" t="n">
         <v>52.9</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -17005,7 +17298,7 @@
       <c r="F56" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="31" t="n">
+      <c r="G56" s="33" t="n">
         <v>51.2</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -17047,7 +17340,7 @@
       <c r="F57" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="31" t="n">
+      <c r="G57" s="33" t="n">
         <v>50.6</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -17089,7 +17382,7 @@
       <c r="F58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G58" s="31" t="n">
+      <c r="G58" s="33" t="n">
         <v>50.3</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -17131,7 +17424,7 @@
       <c r="F59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="31" t="n">
+      <c r="G59" s="33" t="n">
         <v>50.3</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -17173,7 +17466,7 @@
       <c r="F60" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G60" s="31" t="n">
+      <c r="G60" s="33" t="n">
         <v>50.1</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -17215,7 +17508,7 @@
       <c r="F61" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G61" s="31" t="n">
+      <c r="G61" s="33" t="n">
         <v>50</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -17257,7 +17550,7 @@
       <c r="F62" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="31" t="n">
+      <c r="G62" s="33" t="n">
         <v>50</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -17299,7 +17592,7 @@
       <c r="F63" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G63" s="31" t="n">
+      <c r="G63" s="33" t="n">
         <v>50</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -17429,19 +17722,19 @@
           <t>東川町</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
+      <c r="B6" s="34" t="n">
         <v>315</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>56</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="35" t="n">
         <v>109</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>85</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="36" t="n">
         <v>240</v>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -17457,19 +17750,19 @@
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="34" t="n">
         <v>308</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="35" t="n">
         <v>116</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>83</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="36" t="n">
         <v>254</v>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -17485,19 +17778,19 @@
           <t>東神楽町</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
+      <c r="B8" s="34" t="n">
         <v>379</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="35" t="n">
         <v>45</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="36" t="n">
         <v>184</v>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -17610,7 +17903,7 @@
       <c r="F13" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="37" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="H13" s="17" t="n">
@@ -17660,7 +17953,7 @@
       <c r="F14" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="35" t="n">
+      <c r="G14" s="37" t="n">
         <v>47.3</v>
       </c>
       <c r="H14" s="17" t="n">
@@ -17710,7 +18003,7 @@
       <c r="F15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="35" t="n">
+      <c r="G15" s="37" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="H15" s="17" t="n">
@@ -17760,7 +18053,7 @@
       <c r="F16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G16" s="35" t="n">
+      <c r="G16" s="37" t="n">
         <v>87.8</v>
       </c>
       <c r="H16" s="14" t="n">
@@ -17810,7 +18103,7 @@
       <c r="F17" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G17" s="35" t="n">
+      <c r="G17" s="37" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="H17" s="14" t="n">
@@ -17860,7 +18153,7 @@
       <c r="F18" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="35" t="n">
+      <c r="G18" s="37" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="H18" s="14" t="n">
@@ -17910,7 +18203,7 @@
       <c r="F19" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="35" t="n">
+      <c r="G19" s="37" t="n">
         <v>46.1</v>
       </c>
       <c r="H19" s="14" t="n">
@@ -17960,7 +18253,7 @@
       <c r="F20" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G20" s="35" t="n">
+      <c r="G20" s="37" t="n">
         <v>43.1</v>
       </c>
       <c r="H20" s="17" t="n">
@@ -18010,7 +18303,7 @@
       <c r="F21" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="35" t="n">
+      <c r="G21" s="37" t="n">
         <v>74.5</v>
       </c>
       <c r="H21" s="17" t="n">
@@ -18060,7 +18353,7 @@
       <c r="F22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="35" t="n">
+      <c r="G22" s="37" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="H22" s="14" t="n">
@@ -18110,7 +18403,7 @@
       <c r="F23" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="35" t="n">
+      <c r="G23" s="37" t="n">
         <v>48.8</v>
       </c>
       <c r="H23" s="14" t="n">
@@ -18160,7 +18453,7 @@
       <c r="F24" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="35" t="n">
+      <c r="G24" s="37" t="n">
         <v>87</v>
       </c>
       <c r="H24" s="14" t="n">
@@ -18210,7 +18503,7 @@
       <c r="F25" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="35" t="n">
+      <c r="G25" s="37" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="H25" s="17" t="n">
@@ -18260,7 +18553,7 @@
       <c r="F26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="35" t="n">
+      <c r="G26" s="37" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="H26" s="14" t="n">
@@ -18310,7 +18603,7 @@
       <c r="F27" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="35" t="n">
+      <c r="G27" s="37" t="n">
         <v>70.5</v>
       </c>
       <c r="H27" s="14" t="n">
@@ -18356,7 +18649,7 @@
       <c r="F28" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G28" s="35" t="n">
+      <c r="G28" s="37" t="n">
         <v>70.5</v>
       </c>
       <c r="H28" s="14" t="n">
@@ -18402,7 +18695,7 @@
       <c r="F29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="35" t="n">
+      <c r="G29" s="37" t="n">
         <v>70</v>
       </c>
       <c r="H29" s="17" t="n">
@@ -18448,7 +18741,7 @@
       <c r="F30" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="35" t="n">
+      <c r="G30" s="37" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="H30" s="14" t="n">
@@ -18494,7 +18787,7 @@
       <c r="F31" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="35" t="n">
+      <c r="G31" s="37" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="H31" s="14" t="n">
@@ -18540,7 +18833,7 @@
       <c r="F32" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="35" t="n">
+      <c r="G32" s="37" t="n">
         <v>50</v>
       </c>
       <c r="H32" s="14" t="n">
@@ -18586,7 +18879,7 @@
       <c r="F33" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="35" t="n">
+      <c r="G33" s="37" t="n">
         <v>50</v>
       </c>
       <c r="H33" s="17" t="n">
@@ -18632,7 +18925,7 @@
       <c r="F34" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G34" s="35" t="n">
+      <c r="G34" s="37" t="n">
         <v>46.2</v>
       </c>
       <c r="H34" s="17" t="n">
@@ -18678,7 +18971,7 @@
       <c r="F35" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="35" t="n">
+      <c r="G35" s="37" t="n">
         <v>30</v>
       </c>
       <c r="H35" s="14" t="n">
@@ -18724,7 +19017,7 @@
       <c r="F36" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="35" t="n">
+      <c r="G36" s="37" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="H36" s="17" t="n">
@@ -18770,7 +19063,7 @@
       <c r="F37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="35" t="n">
+      <c r="G37" s="37" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="H37" s="17" t="n">
@@ -18816,7 +19109,7 @@
       <c r="F38" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="35" t="n">
+      <c r="G38" s="37" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="H38" s="17" t="n">
@@ -18862,7 +19155,7 @@
       <c r="F39" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="35" t="n">
+      <c r="G39" s="37" t="n">
         <v>83.2</v>
       </c>
       <c r="H39" s="17" t="n">
@@ -18912,7 +19205,7 @@
       <c r="F40" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="35" t="n">
+      <c r="G40" s="37" t="n">
         <v>82.7</v>
       </c>
       <c r="H40" s="14" t="n">
@@ -18958,7 +19251,7 @@
       <c r="F41" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="35" t="n">
+      <c r="G41" s="37" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="H41" s="14" t="n">
@@ -19004,7 +19297,7 @@
       <c r="F42" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="35" t="n">
+      <c r="G42" s="37" t="n">
         <v>81.8</v>
       </c>
       <c r="H42" s="17" t="n">
@@ -19050,7 +19343,7 @@
       <c r="F43" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="35" t="n">
+      <c r="G43" s="37" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="H43" s="17" t="n">
@@ -19096,7 +19389,7 @@
       <c r="F44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="35" t="n">
+      <c r="G44" s="37" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="H44" s="17" t="n">
@@ -19142,7 +19435,7 @@
       <c r="F45" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="35" t="n">
+      <c r="G45" s="37" t="n">
         <v>71.2</v>
       </c>
       <c r="H45" s="17" t="n">
@@ -19188,7 +19481,7 @@
       <c r="F46" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G46" s="35" t="n">
+      <c r="G46" s="37" t="n">
         <v>70</v>
       </c>
       <c r="H46" s="17" t="n">
@@ -19234,7 +19527,7 @@
       <c r="F47" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G47" s="35" t="n">
+      <c r="G47" s="37" t="n">
         <v>70</v>
       </c>
       <c r="H47" s="14" t="n">
@@ -19280,7 +19573,7 @@
       <c r="F48" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="35" t="n">
+      <c r="G48" s="37" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="H48" s="17" t="n">
@@ -19326,7 +19619,7 @@
       <c r="F49" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G49" s="35" t="n">
+      <c r="G49" s="37" t="n">
         <v>61.2</v>
       </c>
       <c r="H49" s="17" t="n">
@@ -19372,7 +19665,7 @@
       <c r="F50" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G50" s="35" t="n">
+      <c r="G50" s="37" t="n">
         <v>50.1</v>
       </c>
       <c r="H50" s="17" t="n">
@@ -19418,7 +19711,7 @@
       <c r="F51" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="35" t="n">
+      <c r="G51" s="37" t="n">
         <v>50.1</v>
       </c>
       <c r="H51" s="17" t="n">
@@ -19464,7 +19757,7 @@
       <c r="F52" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="35" t="n">
+      <c r="G52" s="37" t="n">
         <v>47.7</v>
       </c>
       <c r="H52" s="17" t="n">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜169・169件</t>
+          <t>No.1〜171・171件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜171・171件</t>
+          <t>No.1〜173・173件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3571,7 +3571,7 @@
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本表の内的整合の点検です。1件でも不適合があると作成が終了コード1で終わります。</t>
+          <t>本表の内的整合の点検です。1件でも不適合があると作成を止めます。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜173・173件</t>
+          <t>No.1〜174・174件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜174・174件</t>
+          <t>No.1〜177・177件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜177・177件</t>
+          <t>No.1〜181・181件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜181・181件</t>
+          <t>No.1〜184・184件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜184・184件</t>
+          <t>No.1〜186・186件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜186・186件</t>
+          <t>No.1〜189・189件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜189・189件</t>
+          <t>No.1〜190・190件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜190・190件</t>
+          <t>No.1〜192・192件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">

--- a/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
+++ b/output/第10期計画_交付金評価の取りまとめと第10期への反映.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>No.1〜192・192件</t>
+          <t>No.1〜193・193件</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
